--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,10 +525,15 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>capacity_id</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>project_key_str</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>project_key_tuple</t>
         </is>
@@ -615,10 +620,15 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>prod_DB_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_27777.777777777777</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
@@ -705,10 +715,15 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>prod_DB_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_100000.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
@@ -799,10 +814,15 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>prod_DB_655601d6-44d7-5fae-9f00-aed5f36c0462_20016.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
@@ -891,10 +911,15 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>prod_DB_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
@@ -985,10 +1010,15 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>prod_DB_6d0da839-f19a-5497-8a1f-befe19c9e09b_113031.93000000001</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1079,10 +1109,15 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>prod_DB_6d0da839-f19a-5497-8a1f-befe19c9e09b_156831.93</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1169,10 +1204,15 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>prod_DB_1fba0998-ffe7-54f5-a236-919e234e7829_46387.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>GB|Oxfordshire|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1243,10 +1283,15 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>prod_DB_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_1076.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>GB|None|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1335,10 +1380,15 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>prod_DB_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>GB|Oxfordshire|('arrival',)|vehicle</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
         </is>
@@ -1425,10 +1475,15 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>prod_DB_d005f306-6f24-5243-9c14-757b40e8e259_50339.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
         </is>
@@ -1519,10 +1574,15 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>prod_DB_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_15411.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>DE|Ingolstadt|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
         </is>
@@ -1613,10 +1673,15 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>prod_DB_8c10f625-fea2-51ad-a118-adb9ac7fbea1_28334.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>DE|Neckarsulm|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
         </is>
@@ -1685,10 +1750,15 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>prod_DB_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>FR|None|('byd',)|vehicle</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>('FR', 'None', "('byd',)", 'vehicle')</t>
         </is>
@@ -1767,10 +1837,15 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>prod_DB_87ed39d0-95e7-55f0-9c84-367ea52968ab_400.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
         </is>
@@ -1861,10 +1936,15 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>prod_DB_0ec09a24-125b-5eee-a2c2-db6f7c89e362_250000.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>DE|Cologne|('ford',)|vehicle</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
         </is>
@@ -1951,10 +2031,15 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>prod_DB_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_72052.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>CZ|Nošovice|('hyundai',)|vehicle</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
         </is>
@@ -2041,10 +2126,15 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>prod_DB_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_37239.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>SK|Žilina Region|('kia',)|vehicle</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
         </is>
@@ -2131,10 +2221,15 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>prod_DB_303ad2bc-a853-55e8-9566-858510f8d770_18427.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>DE|Bremen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2205,10 +2300,15 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>prod_DB_5adfe1a0-5af6-579e-b8fc-45382ca79c99_4760.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2277,10 +2377,15 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>prod_DB_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2371,10 +2476,15 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>prod_DB_728fcd34-e11b-59cc-ac72-f6f4bfd53540_83195.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2465,10 +2575,15 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>prod_DB_1a71a177-e936-50c5-9103-940e7397cc66_62577.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2539,10 +2654,15 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>prod_DB_c1ab1fd2-af88-5319-8d29-f5f844946c36_10739.0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>ES|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2621,10 +2741,15 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>prod_DB_792aa593-f545-506e-876a-c8156d0c4131_50444.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2707,10 +2832,15 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
+          <t>prod_DB_f119dc73-a41d-541d-96ec-a7f18a74dcab_40710.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>GB|Sunderland|('nissan',)|vehicle</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
         </is>
@@ -2791,10 +2921,15 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>prod_DB_916f228d-de7f-5acb-9645-66e4b8495022_nan</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>HR|Krapina-Zagorje|('rimac automobili',)|vehicle</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>('HR', 'Krapina-Zagorje', "('rimac automobili',)", 'vehicle')</t>
         </is>
@@ -2881,10 +3016,15 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
+          <t>prod_DB_f2de5535-0d2e-5fe4-971b-d70bcab45f62_20135.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>ES|Catalonia|('seat',)|vehicle</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>('ES', 'Catalonia', "('seat',)", 'vehicle')</t>
         </is>
@@ -2971,10 +3111,15 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>prod_DB_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_79507.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
@@ -3059,10 +3204,15 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>prod_DB_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_nan</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
@@ -3149,10 +3299,15 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>prod_DB_b4cab349-dacc-5f73-8e7b-483f322893e7_9653.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3237,10 +3392,15 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>prod_DB_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3327,10 +3487,15 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>prod_DB_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_49264.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3415,10 +3580,15 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>prod_DB_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3505,10 +3675,15 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>prod_DB_408c902f-cfa7-504a-9977-6439e267cf6f_3734.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3593,10 +3768,15 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>prod_DB_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -3683,10 +3863,15 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>prod_DB_ab942289-b19a-5128-8112-1c5a42e60372_206097.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>DE|Berlin|('tesla',)|vehicle</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
         </is>
@@ -3767,10 +3952,15 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>prod_DB_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
         </is>
@@ -3849,10 +4039,15 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
+          <t>prod_DB_24f54170-5f2a-500a-8994-da2daf36ed6a_94839.0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
         </is>
@@ -3939,10 +4134,15 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>prod_DB_5407b64f-8759-5926-9898-d6b7600bdfe1_333000.0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>DE|Zwickau|('volkswagen',)|vehicle</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
         </is>
@@ -4011,10 +4211,15 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
+          <t>prod_DB_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>FR|None|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
         </is>
@@ -4103,10 +4308,15 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>prod_DB_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>
@@ -4195,10 +4405,15 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
+          <t>prod_DB_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>
@@ -4283,10 +4498,15 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
+          <t>prod_DB_43827abe-ea8c-5a39-87d9-c1114db92c51_nan</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>SE|Västra Götaland|('volvo',)|vehicle</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
         </is>
@@ -4373,10 +4593,15 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>prod_DB_e2b88591-16ed-593d-81d0-f4437853d855_14287.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>GB|Knowsley|('tata jlr',)|vehicle</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
         </is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,26 +542,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27777.77777777778</v>
+        <v>40000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>41535</v>
+        <v>45657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,75 +588,67 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Kreisfreie Stadt Leipzig</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>51.33962</v>
+        <v>47.68333</v>
       </c>
       <c r="P2" t="n">
-        <v>12.37129</v>
+        <v>17.63512</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
+          <t>696036ed-ca14-5c3f-87d3-afbe17e5e286</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>prod_DB_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_27777.777777777777</t>
+          <t>68d684fc1c2e9d8ed1487afa_696036ed-ca14-5c3f-87d3-afbe17e5e286_40000.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>DE|Leipzig|('bmw',)|vehicle</t>
+          <t>HU|Győr-Moson-Sopron|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
+          <t>('HU', 'Győr-Moson-Sopron', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -665,11 +657,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45355</v>
+        <v>45657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -683,75 +675,79 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Maubeuge</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Leipzig</t>
+          <t>Arrondissement of Avesnes-sur-Helpe</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>51.33962</v>
+        <v>50.27875</v>
       </c>
       <c r="P3" t="n">
-        <v>12.37129</v>
+        <v>3.97267</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
+          <t>6630540c-9bc6-541b-a124-85fbb4865ffd</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>prod_DB_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_100000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6630540c-9bc6-541b-a124-85fbb4865ffd_40000.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DE|Leipzig|('bmw',)|vehicle</t>
+          <t>FR|Maubeuge|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'Maubeuge', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20016</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -764,7 +760,7 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42185</v>
+        <v>45657</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -778,78 +774,80 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Meurthe et Moselle</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Munich, Urban District</t>
+          <t>Arrondissement of Briey</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>48.13743</v>
+        <v>49.17372</v>
       </c>
       <c r="P4" t="n">
-        <v>11.57549</v>
+        <v>5.96869</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
+          <t>7c1498d5-0289-5c56-a848-588df51f6771</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>prod_DB_655601d6-44d7-5fae-9f00-aed5f36c0462_20016.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7c1498d5-0289-5c56-a848-588df51f6771_0.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>DE|Munich|('bmw',)|vehicle</t>
+          <t>FR|Batilly|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'Batilly', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40000</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>operational</t>
@@ -857,11 +855,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>44491</v>
+        <v>45291</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -875,79 +873,79 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Munich, Urban District</t>
+          <t>Arrondissement of Mantes-la-Jolie</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>48.13743</v>
+        <v>48.96523</v>
       </c>
       <c r="P5" t="n">
-        <v>11.57549</v>
+        <v>1.87314</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
+          <t>efa6f6c1-a5b5-5aad-bffe-b3e85d787636</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>prod_DB_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_efa6f6c1-a5b5-5aad-bffe-b3e85d787636_40000.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>DE|Munich|('bmw',)|vehicle</t>
+          <t>FR|Flins-sur-Seine|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>113031.93</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -956,11 +954,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>44876</v>
+        <v>45657</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -974,79 +972,79 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Sandouville</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Upper Palatinate</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Arrondissement of Le Havre</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Sandouville</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>49.01513</v>
+        <v>49.4978</v>
       </c>
       <c r="P6" t="n">
-        <v>12.10161</v>
+        <v>0.31748</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
+          <t>fce8c5b2-5e51-5d37-85d6-3ceea490a597</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>prod_DB_6d0da839-f19a-5497-8a1f-befe19c9e09b_113031.93000000001</t>
+          <t>68d684fc1c2e9d8ed1487afa_fce8c5b2-5e51-5d37-85d6-3ceea490a597_0.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DE|Regensburg|('bmw',)|vehicle</t>
+          <t>FR|Sandouville|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'Sandouville', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>156831.93</v>
+        <v>120000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1055,11 +1053,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45744</v>
+        <v>45657</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1073,53 +1071,53 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Upper Palatinate</t>
+          <t>North</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Arrondissement of Douai</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>49.01513</v>
+        <v>50.37069</v>
       </c>
       <c r="P7" t="n">
-        <v>12.10161</v>
+        <v>3.07922</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
+          <t>f8b79f53-25f2-516c-8983-966d79119fdc</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>prod_DB_6d0da839-f19a-5497-8a1f-befe19c9e09b_156831.93</t>
+          <t>68d684fc1c2e9d8ed1487afa_f8b79f53-25f2-516c-8983-966d79119fdc_120000.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>DE|Regensburg|('bmw',)|vehicle</t>
+          <t>FR|Douai|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'Douai', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1131,21 +1129,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>46387</v>
+        <v>180000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1154,11 +1152,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>43655</v>
+        <v>45657</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1172,49 +1170,53 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Dingolfing</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Lower Bavaria</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oxford</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Landkreis Dingolfing-Landau</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Dingolfing</t>
+        </is>
+      </c>
       <c r="O8" t="n">
-        <v>51.73213</v>
+        <v>48.64244</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.20631</v>
+        <v>12.49283</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
+          <t>daf49ae1-44a2-5e11-a257-ab0a1d11d24b</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>prod_DB_1fba0998-ffe7-54f5-a236-919e234e7829_46387.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_daf49ae1-44a2-5e11-a257-ab0a1d11d24b_180000.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('bmw',)|vehicle</t>
+          <t>DE|Dingolfing|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Dingolfing', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1226,21 +1228,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>goodwood (rolls-royce manufacturing)</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goodwood_rollsroyce_manufacturing</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1076</v>
+        <v>40000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1253,7 +1255,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45291</v>
+        <v>41535</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1265,72 +1267,90 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Leipzig</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>51.33962</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.37129</v>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
+          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>prod_DB_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_1076.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_40000.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>GB|None|('bmw',)|vehicle</t>
+          <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>160000</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>44249</v>
+        <v>45355</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1344,92 +1364,88 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Cherwell District</t>
+          <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>51.89998</v>
+        <v>51.33962</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.15357</v>
+        <v>12.37129</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
+          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>prod_DB_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_160000.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('arrival',)|vehicle</t>
+          <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
+          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50339</v>
+        <v>40000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>43252</v>
+        <v>42185</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1443,66 +1459,70 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Bruxelles-Capitale</t>
+          <t>Upper Bavaria</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Munich, Urban District</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
       <c r="O11" t="n">
-        <v>50.85045</v>
+        <v>48.13743</v>
       </c>
       <c r="P11" t="n">
-        <v>4.34878</v>
+        <v>11.57549</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
+          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>prod_DB_d005f306-6f24-5243-9c14-757b40e8e259_50339.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_40000.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
+          <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1510,9 +1530,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>15411</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>operational</t>
@@ -1520,11 +1538,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45292</v>
+        <v>44491</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1538,7 +1556,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1548,60 +1566,60 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Ingolstadt</t>
+          <t>Munich, Urban District</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>48.76508</v>
+        <v>48.13743</v>
       </c>
       <c r="P12" t="n">
-        <v>11.42372</v>
+        <v>11.57549</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
+          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>prod_DB_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_15411.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>DE|Ingolstadt|('audi',)|vehicle</t>
+          <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1610,7 +1628,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28334</v>
+        <v>160000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1619,11 +1637,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>43983</v>
+        <v>44876</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1637,90 +1655,92 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Regierungsbezirk Stuttgart</t>
+          <t>Upper Palatinate</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Landkreis Heilbronn</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>49.18912</v>
+        <v>49.01513</v>
       </c>
       <c r="P13" t="n">
-        <v>9.22527</v>
+        <v>12.10161</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
+          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>prod_DB_8c10f625-fea2-51ad-a118-adb9ac7fbea1_28334.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_160000.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>DE|Neckarsulm|('audi',)|vehicle</t>
+          <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>240000</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>43440</v>
+        <v>45744</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1732,61 +1752,81 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Upper Palatinate</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>49.01513</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12.10161</v>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
+          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>prod_DB_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_240000.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>FR|None|('byd',)|vehicle</t>
+          <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('byd',)", 'vehicle')</t>
+          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>400</v>
+        <v>80000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,11 +1835,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>42855</v>
+        <v>43655</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1813,67 +1853,75 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>47.74318</v>
+        <v>51.73213</v>
       </c>
       <c r="P15" t="n">
-        <v>18.11913</v>
+        <v>-1.20631</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
+          <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>prod_DB_87ed39d0-95e7-55f0-9c84-367ea52968ab_400.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_1fba0998-ffe7-54f5-a236-919e234e7829_80000.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
+          <t>GB|Oxfordshire|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1882,11 +1930,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45447</v>
+        <v>45291</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1898,85 +1946,63 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Cologne District</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Cologne, Urban District</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>50.93333</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.95</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
+          <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>prod_DB_0ec09a24-125b-5eee-a2c2-db6f7c89e362_250000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_0.0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>DE|Cologne|('ford',)|vehicle</t>
+          <t>GB|None|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
+          <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hyundai</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>bicester</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>bicester</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>72052</v>
-      </c>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1985,7 +2011,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>43891</v>
+        <v>44249</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1999,88 +2025,92 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Nošovice</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Okres Frýdek-Místek</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Nošovice</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>Cherwell District</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Bicester</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>49.66073</v>
+        <v>51.89998</v>
       </c>
       <c r="P17" t="n">
-        <v>18.42633</v>
+        <v>-1.15357</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
+          <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>prod_DB_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_72052.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>CZ|Nošovice|('hyundai',)|vehicle</t>
+          <t>GB|Oxfordshire|('arrival',)|vehicle</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kia</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37239</v>
+        <v>80000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>43831</v>
+        <v>43252</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2094,66 +2124,66 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Žilina Region</t>
+          <t>Arrondissement Brussel-Hoofdstad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Žilina District</t>
+          <t>Bruxelles-Capitale</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Arrondissement Brussel-Hoofdstad</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>49.22315</v>
+        <v>50.85045</v>
       </c>
       <c r="P18" t="n">
-        <v>18.73941</v>
+        <v>4.34878</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
+          <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>prod_DB_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_37239.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_d005f306-6f24-5243-9c14-757b40e8e259_80000.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK|Žilina Region|('kia',)|vehicle</t>
+          <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2162,7 +2192,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18427</v>
+        <v>20000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2175,7 +2205,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42005</v>
+        <v>45292</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2189,66 +2219,70 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Bremen</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Upper Bavaria</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Bremen</t>
+          <t>Kreisfreie Stadt Ingolstadt</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>53.07582</v>
+        <v>48.76508</v>
       </c>
       <c r="P19" t="n">
-        <v>8.807169999999999</v>
+        <v>11.42372</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
+          <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>prod_DB_303ad2bc-a853-55e8-9566-858510f8d770_18427.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_20000.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>DE|Bremen|('mercedes benz',)|vehicle</t>
+          <t>DE|Ingolstadt|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2257,7 +2291,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4760</v>
+        <v>40000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2266,11 +2300,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>43831</v>
+        <v>43983</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2282,72 +2316,92 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Neckarsulm</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Stuttgart</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Landkreis Heilbronn</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Neckarsulm</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>49.18912</v>
+      </c>
+      <c r="P20" t="n">
+        <v>9.22527</v>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>prod_DB_5adfe1a0-5af6-579e-b8fc-45382ca79c99_4760.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_8c10f625-fea2-51ad-a118-adb9ac7fbea1_40000.0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>DE|Neckarsulm|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>allone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>allone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45261</v>
+        <v>43440</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2367,53 +2421,53 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>prod_DB_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>FR|None|('byd',)|vehicle</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('FR', 'None', "('byd',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>komárom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>komárom</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>83195</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2422,11 +2476,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43102</v>
+        <v>42855</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2440,70 +2494,58 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Rastatt</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Karlsruhe Region</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Landkreis Rastatt</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Rastatt</t>
-        </is>
-      </c>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>48.85851</v>
+        <v>47.74318</v>
       </c>
       <c r="P22" t="n">
-        <v>8.20965</v>
+        <v>18.11913</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
+          <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>prod_DB_728fcd34-e11b-59cc-ac72-f6f4bfd53540_83195.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_87ed39d0-95e7-55f0-9c84-367ea52968ab_0.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
+          <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
+          <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>cologne</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>cologne</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2512,7 +2554,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>62577.5</v>
+        <v>360000</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2525,7 +2567,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>42370</v>
+        <v>45447</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2539,79 +2581,79 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Regierungsbezirk Stuttgart</t>
+          <t>Cologne District</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Landkreis Böblingen</t>
+          <t>Cologne, Urban District</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>48.7</v>
+        <v>50.93333</v>
       </c>
       <c r="P23" t="n">
-        <v>9.01667</v>
+        <v>6.95</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
+          <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>prod_DB_1a71a177-e936-50c5-9103-940e7397cc66_62577.5</t>
+          <t>68d684fc1c2e9d8ed1487afa_0ec09a24-125b-5eee-a2c2-db6f7c89e362_360000.0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
+          <t>DE|Cologne|('ford',)|vehicle</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>hyundai</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10739</v>
+        <v>120000</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2624,7 +2666,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>43617</v>
+        <v>43891</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2636,61 +2678,77 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Nošovice</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Okres Frýdek-Místek</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Nošovice</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>49.66073</v>
+      </c>
+      <c r="P24" t="n">
+        <v>18.42633</v>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
+          <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>prod_DB_c1ab1fd2-af88-5319-8d29-f5f844946c36_10739.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_120000.0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>ES|None|('mercedes benz',)|vehicle</t>
+          <t>CZ|Nošovice|('hyundai',)|vehicle</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>kia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>50444</v>
+        <v>60000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2703,7 +2761,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>44530</v>
+        <v>43831</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2717,67 +2775,75 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Bács-Kiskun</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>Žilina Region</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Žilina District</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>46.90618</v>
+        <v>49.22315</v>
       </c>
       <c r="P25" t="n">
-        <v>19.69128</v>
+        <v>18.73941</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>792aa593-f545-506e-876a-c8156d0c4131</t>
+          <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>prod_DB_792aa593-f545-506e-876a-c8156d0c4131_50444.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_60000.0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
+          <t>SK|Žilina Region|('kia',)|vehicle</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
+          <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>40710</v>
+        <v>40000</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2786,11 +2852,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41275</v>
+        <v>42005</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2804,70 +2870,76 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Bremen</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
       <c r="O26" t="n">
-        <v>54.90465</v>
+        <v>53.07582</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.38222</v>
+        <v>8.807169999999999</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
+          <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>prod_DB_f119dc73-a41d-541d-96ec-a7f18a74dcab_40710.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_303ad2bc-a853-55e8-9566-858510f8d770_40000.0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>GB|Sunderland|('nissan',)|vehicle</t>
+          <t>DE|Bremen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
+          <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rimac automobili</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>veliko trgovišće</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>veliko_trgovišće</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>operational</t>
@@ -2879,7 +2951,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45583</v>
+        <v>43831</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2891,74 +2963,60 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Krapina-Zagorje</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Municipality of Veliko Trgovišće</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>46</v>
-      </c>
-      <c r="P27" t="n">
-        <v>15.85</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>916f228d-de7f-5acb-9645-66e4b8495022</t>
+          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>prod_DB_916f228d-de7f-5acb-9645-66e4b8495022_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_0.0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>HR|Krapina-Zagorje|('rimac automobili',)|vehicle</t>
+          <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>('HR', 'Krapina-Zagorje', "('rimac automobili',)", 'vehicle')</t>
+          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>martorell</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>martorell</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>20135</v>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>operational</t>
@@ -2966,11 +3024,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>43831</v>
+        <v>45261</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2982,77 +3040,61 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Catalonia</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Martorell</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>41.47402</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.93062</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>f2de5535-0d2e-5fe4-971b-d70bcab45f62</t>
+          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>prod_DB_f2de5535-0d2e-5fe4-971b-d70bcab45f62_20135.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>ES|Catalonia|('seat',)|vehicle</t>
+          <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>('ES', 'Catalonia', "('seat',)", 'vehicle')</t>
+          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>skoda</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mladá boleslav</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mladá_boleslav</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>79507</v>
+        <v>120000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3065,7 +3107,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>44075</v>
+        <v>43102</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3079,74 +3121,80 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Rastatt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Mladá Boleslav District</t>
+          <t>Karlsruhe Region</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Landkreis Rastatt</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Rastatt</t>
+        </is>
+      </c>
       <c r="O29" t="n">
-        <v>50.41135</v>
+        <v>48.85851</v>
       </c>
       <c r="P29" t="n">
-        <v>14.90318</v>
+        <v>8.20965</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
+          <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>prod_DB_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_79507.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_728fcd34-e11b-59cc-ac72-f6f4bfd53540_120000.0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
+          <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
+          <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>skoda</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mladá boleslav</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mladá_boleslav</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>80000</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3154,11 +3202,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45679</v>
+        <v>42370</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3172,75 +3220,79 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sindelfingen</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Mladá Boleslav District</t>
+          <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Landkreis Böblingen</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Sindelfingen</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>50.41135</v>
+        <v>48.7</v>
       </c>
       <c r="P30" t="n">
-        <v>14.90318</v>
+        <v>9.01667</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
+          <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>prod_DB_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_1a71a177-e936-50c5-9103-940e7397cc66_80000.0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
+          <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
+          <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>vitoria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>vitoria</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9653</v>
+        <v>20000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3253,7 +3305,7 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43831</v>
+        <v>43617</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3265,76 +3317,62 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Wartburgkreis</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>50.9807</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10.31522</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
+          <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>prod_DB_b4cab349-dacc-5f73-8e7b-483f322893e7_9653.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_c1ab1fd2-af88-5319-8d29-f5f844946c36_20000.0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>DE|Eisenach|('stellantis',)|vehicle</t>
+          <t>ES|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
+          <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>80000</v>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3342,11 +3380,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45536</v>
+        <v>44530</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3360,88 +3398,80 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Bács-Kiskun</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Wartburgkreis</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>50.9807</v>
+        <v>46.90618</v>
       </c>
       <c r="P32" t="n">
-        <v>10.31522</v>
+        <v>19.69128</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
+          <t>792aa593-f545-506e-876a-c8156d0c4131</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>prod_DB_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_792aa593-f545-506e-876a-c8156d0c4131_80000.0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>DE|Eisenach|('stellantis',)|vehicle</t>
+          <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
+          <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49264</v>
+        <v>60000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43559</v>
+        <v>41275</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3455,86 +3485,82 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Trnava District</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Trnava</t>
-        </is>
-      </c>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>48.37741</v>
+        <v>54.90465</v>
       </c>
       <c r="P33" t="n">
-        <v>17.58723</v>
+        <v>-1.38222</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
+          <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>prod_DB_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_49264.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f119dc73-a41d-541d-96ec-a7f18a74dcab_60000.0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
+          <t>GB|Sunderland|('nissan',)|vehicle</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
+          <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>rimac automobili</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>veliko trgovišće</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>veliko_trgovišće</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45108</v>
+        <v>45583</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3548,66 +3574,62 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Krapina-Zagorje</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Trnava District</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Trnava</t>
-        </is>
-      </c>
+          <t>Municipality of Veliko Trgovišće</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>48.37741</v>
+        <v>46</v>
       </c>
       <c r="P34" t="n">
-        <v>17.58723</v>
+        <v>15.85</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
+          <t>916f228d-de7f-5acb-9645-66e4b8495022</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>prod_DB_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_916f228d-de7f-5acb-9645-66e4b8495022_nan</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
+          <t>HR|Krapina-Zagorje|('rimac automobili',)|vehicle</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
+          <t>('HR', 'Krapina-Zagorje', "('rimac automobili',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>martorell</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>martorell</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3616,7 +3638,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3734</v>
+        <v>40000</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3629,7 +3651,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>41061</v>
+        <v>43831</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3643,74 +3665,76 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Martorell</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>42.23282</v>
+        <v>41.47402</v>
       </c>
       <c r="P35" t="n">
-        <v>-8.72264</v>
+        <v>1.93062</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
+          <t>f2de5535-0d2e-5fe4-971b-d70bcab45f62</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>prod_DB_408c902f-cfa7-504a-9977-6439e267cf6f_3734.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f2de5535-0d2e-5fe4-971b-d70bcab45f62_40000.0</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>ES|Galicia|('stellantis',)|vehicle</t>
+          <t>ES|Catalonia|('seat',)|vehicle</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
+          <t>('ES', 'Catalonia', "('seat',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>skoda</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>mladá boleslav</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>mladá_boleslav</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>120000</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3718,11 +3742,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44502</v>
+        <v>44075</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3736,76 +3760,74 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Mladá Boleslav District</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>42.23282</v>
+        <v>50.41135</v>
       </c>
       <c r="P36" t="n">
-        <v>-8.72264</v>
+        <v>14.90318</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
+          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>prod_DB_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_120000.0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>ES|Galicia|('stellantis',)|vehicle</t>
+          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
+          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>skoda</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>mladá boleslav</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>mladá_boleslav</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>206097</v>
-      </c>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3813,11 +3835,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>44642</v>
+        <v>45679</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3831,77 +3853,79 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Mladá Boleslav District</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Berlin, Stadt</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>52.52437</v>
+        <v>50.41135</v>
       </c>
       <c r="P37" t="n">
-        <v>13.41053</v>
+        <v>14.90318</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
+          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>prod_DB_ab942289-b19a-5128-8112-1c5a42e60372_206097.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_nan</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>DE|Berlin|('tesla',)|vehicle</t>
+          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
+          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3910,7 +3934,7 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>42157</v>
+        <v>43831</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3924,72 +3948,74 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Tilburg Municipality</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Tilburg Municipality</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Eisenach</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Wartburgkreis</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
       <c r="O38" t="n">
-        <v>51.55551</v>
+        <v>50.9807</v>
       </c>
       <c r="P38" t="n">
-        <v>5.0913</v>
+        <v>10.31522</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
+          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>prod_DB_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_0.0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
+          <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
+          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>94839</v>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3997,11 +4023,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>41426</v>
+        <v>45536</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4015,80 +4041,88 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Eisenach</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Wartburgkreis</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
       <c r="O39" t="n">
-        <v>48.14816</v>
+        <v>50.9807</v>
       </c>
       <c r="P39" t="n">
-        <v>17.10674</v>
+        <v>10.31522</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
+          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>prod_DB_24f54170-5f2a-500a-8994-da2daf36ed6a_94839.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
+          <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
+          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>333000</v>
+        <v>80000</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43773</v>
+        <v>43559</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4102,86 +4136,86 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Zwickau</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Trnava District</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Zwickau</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Zwickau</t>
-        </is>
-      </c>
+          <t>Trnava</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>50.72724</v>
+        <v>48.37741</v>
       </c>
       <c r="P40" t="n">
-        <v>12.48839</v>
+        <v>17.58723</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
+          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>prod_DB_5407b64f-8759-5926-9898-d6b7600bdfe1_333000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_80000.0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>DE|Zwickau|('volkswagen',)|vehicle</t>
+          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
+          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>volvo group</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>blainville</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>blainville</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43646</v>
+        <v>45108</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4193,60 +4227,78 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Trnava District</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Trnava</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>48.37741</v>
+      </c>
+      <c r="P41" t="n">
+        <v>17.58723</v>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
+          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>prod_DB_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>FR|None|('volvo group',)|vehicle</t>
+          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
+          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>volvo group</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4258,7 +4310,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45183</v>
+        <v>41061</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4272,81 +4324,77 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>East Flanders Province</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>51.05</v>
+        <v>42.23282</v>
       </c>
       <c r="P42" t="n">
-        <v>3.71667</v>
+        <v>-8.72264</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>prod_DB_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_0.0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>volvo group</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4355,7 +4403,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45777</v>
+        <v>44502</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4369,90 +4417,88 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>East Flanders Province</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>51.05</v>
+        <v>42.23282</v>
       </c>
       <c r="P43" t="n">
-        <v>3.71667</v>
+        <v>-8.72264</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>prod_DB_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>volvo</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>mulhouse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>mulhouse</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>60000</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45717</v>
+        <v>45291</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4466,142 +4512,1274 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Västra Götaland</t>
+          <t>Mulhouse</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Torslanda</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>Arrondissement of Mulhouse</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
       <c r="O44" t="n">
-        <v>57.72504</v>
+        <v>47.75205</v>
       </c>
       <c r="P44" t="n">
-        <v>11.76903</v>
+        <v>7.32866</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>prod_DB</t>
+          <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>43827abe-ea8c-5a39-87d9-c1114db92c51</t>
+          <t>f04e6321-7663-5242-a582-e78bf30492fb</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>prod_DB_43827abe-ea8c-5a39-87d9-c1114db92c51_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_f04e6321-7663-5242-a582-e78bf30492fb_60000.0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>SE|Västra Götaland|('volvo',)|vehicle</t>
+          <t>FR|Mulhouse|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
+          <t>('FR', 'Mulhouse', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Arrondissement of Rennes</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>48.11198</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-1.67429</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0f1addfd-3731-5deb-905c-c1ca76aa8f8b</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_0f1addfd-3731-5deb-905c-c1ca76aa8f8b_20000.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>FR|Rennes|('stellantis',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>('FR', 'Rennes', "('stellantis',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sochaux</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sochaux</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>retrofit</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Doubs</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Arrondissement of Montbéliard</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>47.50808</v>
+      </c>
+      <c r="P46" t="n">
+        <v>6.82748</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>69c19e84-42f0-5366-8453-cb02017d6f48</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_69c19e84-42f0-5366-8453-cb02017d6f48_40000.0</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>FR|Sochaux|('stellantis',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>('FR', 'Sochaux', "('stellantis',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stellantis (fiat chrysler)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>hordain</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>hordain</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Hordain</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Arrondissement of Valenciennes</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Hordain</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>50.26306</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3.31358</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>6cf38a0c-36de-551b-9bcc-3cca04da0224</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_6cf38a0c-36de-551b-9bcc-3cca04da0224_40000.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>FR|Hordain|('stellantis (fiat chrysler)',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>('FR', 'Hordain', "('stellantis (fiat chrysler)',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>srellantis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>poissy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>poissy</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Poissy</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Yvelines</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Arrondissement of Saint-Germain-en-Laye</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Poissy</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>48.92902</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.04952</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>f0462b5a-ae72-5815-9d01-c0d999befd85</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_f0462b5a-ae72-5815-9d01-c0d999befd85_40000.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>FR|Poissy|('srellantis',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>('FR', 'Poissy', "('srellantis',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>berlin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>berlin</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>44642</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Berlin, Stadt</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>52.52437</v>
+      </c>
+      <c r="P49" t="n">
+        <v>13.41053</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_ab942289-b19a-5128-8112-1c5a42e60372_320000.0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>DE|Berlin|('tesla',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tilburg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>tilburg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>42157</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Tilburg Municipality</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Tilburg Municipality</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>51.55551</v>
+      </c>
+      <c r="P50" t="n">
+        <v>5.0913</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>bratislava</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bratislava</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>41426</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>48.14816</v>
+      </c>
+      <c r="P51" t="n">
+        <v>17.10674</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_24f54170-5f2a-500a-8994-da2daf36ed6a_140000.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>zwickau</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>zwickau</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>retrofit</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>43773</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>50.72724</v>
+      </c>
+      <c r="P52" t="n">
+        <v>12.48839</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_5407b64f-8759-5926-9898-d6b7600bdfe1_500000.0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>DE|Zwickau|('volkswagen',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>volvo group</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>blainville</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>blainville</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>43646</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>FR|None|('volvo group',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>volvo group</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>45183</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>East Flanders Province</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3.71667</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>volvo group</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>East Flanders Province</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.71667</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>volvo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>torslanda</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>torslanda</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Gothenburg Municipality</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Torslanda</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>57.72504</v>
+      </c>
+      <c r="P56" t="n">
+        <v>11.76903</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>43827abe-ea8c-5a39-87d9-c1114db92c51</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_43827abe-ea8c-5a39-87d9-c1114db92c51_120000.0</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>SE|Västra Götaland|('volvo',)|vehicle</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>tata jlr</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>halewood</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>halewood</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>14287</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E57" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>greenfield</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>vehicle</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>electric</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Knowsley</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Knowsley</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Halewood</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
         <v>53.36434</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P57" t="n">
         <v>-2.82053</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>prod_DB</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>e2b88591-16ed-593d-81d0-f4437853d855</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>prod_DB_e2b88591-16ed-593d-81d0-f4437853d855_14287.0</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_e2b88591-16ed-593d-81d0-f4437853d855_20000.0</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
         <is>
           <t>GB|Knowsley|('tata jlr',)|vehicle</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
         </is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -542,39 +542,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>győr</t>
+          <t>bicester</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>győr</t>
+          <t>bicester</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>40000</v>
-      </c>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45657</v>
+        <v>44249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,17 +586,29 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cherwell District</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bicester</t>
+        </is>
+      </c>
       <c r="O2" t="n">
-        <v>47.68333</v>
+        <v>51.89998</v>
       </c>
       <c r="P2" t="n">
-        <v>17.63512</v>
+        <v>-1.15357</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -607,44 +617,44 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>696036ed-ca14-5c3f-87d3-afbe17e5e286</t>
+          <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_696036ed-ca14-5c3f-87d3-afbe17e5e286_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HU|Győr-Moson-Sopron|('audi',)|vehicle</t>
+          <t>GB|Oxfordshire|('arrival',)|vehicle</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>('HU', 'Győr-Moson-Sopron', "('audi',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>maubeuge</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maubeuge</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -675,29 +685,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Maubeuge</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Arrondissement of Avesnes-sur-Helpe</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Maubeuge</t>
-        </is>
-      </c>
+          <t>Győr-Moson-Sopron</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>50.27875</v>
+        <v>47.68333</v>
       </c>
       <c r="P3" t="n">
-        <v>3.97267</v>
+        <v>17.63512</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -706,61 +704,61 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6630540c-9bc6-541b-a124-85fbb4865ffd</t>
+          <t>696036ed-ca14-5c3f-87d3-afbe17e5e286</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6630540c-9bc6-541b-a124-85fbb4865ffd_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_696036ed-ca14-5c3f-87d3-afbe17e5e286_40000.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FR|Maubeuge|('renault',)|vehicle</t>
+          <t>HU|Győr-Moson-Sopron|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>('FR', 'Maubeuge', "('renault',)", 'vehicle')</t>
+          <t>('HU', 'Győr-Moson-Sopron', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45657</v>
+        <v>43252</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -774,29 +772,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Arrondissement Brussel-Hoofdstad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Meurthe et Moselle</t>
+          <t>Bruxelles-Capitale</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Arrondissement of Briey</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Batilly</t>
-        </is>
-      </c>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>49.17372</v>
+        <v>50.85045</v>
       </c>
       <c r="P4" t="n">
-        <v>5.96869</v>
+        <v>4.34878</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -805,48 +799,48 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7c1498d5-0289-5c56-a848-588df51f6771</t>
+          <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7c1498d5-0289-5c56-a848-588df51f6771_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_d005f306-6f24-5243-9c14-757b40e8e259_80000.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>FR|Batilly|('renault',)|vehicle</t>
+          <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>('FR', 'Batilly', "('renault',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flins</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flins</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -855,11 +849,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45291</v>
+        <v>45292</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -873,29 +867,29 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Flins-sur-Seine</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Upper Bavaria</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Arrondissement of Mantes-la-Jolie</t>
+          <t>Kreisfreie Stadt Ingolstadt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Flins-sur-Seine</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>48.96523</v>
+        <v>48.76508</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87314</v>
+        <v>11.42372</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -904,48 +898,48 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>efa6f6c1-a5b5-5aad-bffe-b3e85d787636</t>
+          <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_efa6f6c1-a5b5-5aad-bffe-b3e85d787636_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_20000.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FR|Flins-sur-Seine|('renault',)|vehicle</t>
+          <t>DE|Ingolstadt|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>('FR', 'Flins-sur-Seine', "('renault',)", 'vehicle')</t>
+          <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -954,11 +948,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45657</v>
+        <v>43983</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -972,29 +966,29 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Neckarsulm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Arrondissement of Le Havre</t>
+          <t>Landkreis Heilbronn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Neckarsulm</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>49.4978</v>
+        <v>49.18912</v>
       </c>
       <c r="P6" t="n">
-        <v>0.31748</v>
+        <v>9.22527</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1003,48 +997,48 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>fce8c5b2-5e51-5d37-85d6-3ceea490a597</t>
+          <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_fce8c5b2-5e51-5d37-85d6-3ceea490a597_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_8c10f625-fea2-51ad-a118-adb9ac7fbea1_40000.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FR|Sandouville|('renault',)|vehicle</t>
+          <t>DE|Neckarsulm|('audi',)|vehicle</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>('FR', 'Sandouville', "('renault',)", 'vehicle')</t>
+          <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1053,7 +1047,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -1071,29 +1065,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Dingolfing</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Lower Bavaria</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Arrondissement of Douai</t>
+          <t>Landkreis Dingolfing-Landau</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Dingolfing</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>50.37069</v>
+        <v>48.64244</v>
       </c>
       <c r="P7" t="n">
-        <v>3.07922</v>
+        <v>12.49283</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1102,22 +1096,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>f8b79f53-25f2-516c-8983-966d79119fdc</t>
+          <t>daf49ae1-44a2-5e11-a257-ab0a1d11d24b</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f8b79f53-25f2-516c-8983-966d79119fdc_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_daf49ae1-44a2-5e11-a257-ab0a1d11d24b_180000.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FR|Douai|('renault',)|vehicle</t>
+          <t>DE|Dingolfing|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>('FR', 'Douai', "('renault',)", 'vehicle')</t>
+          <t>('DE', 'Dingolfing', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1123,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dingolfing</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dingolfing</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1143,7 +1137,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>180000</v>
+        <v>40000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1152,11 +1146,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45657</v>
+        <v>41535</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1170,29 +1164,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dingolfing</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Lower Bavaria</t>
-        </is>
-      </c>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Landkreis Dingolfing-Landau</t>
+          <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Dingolfing</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>48.64244</v>
+        <v>51.33962</v>
       </c>
       <c r="P8" t="n">
-        <v>12.49283</v>
+        <v>12.37129</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1201,22 +1191,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>daf49ae1-44a2-5e11-a257-ab0a1d11d24b</t>
+          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_daf49ae1-44a2-5e11-a257-ab0a1d11d24b_180000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_40000.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>DE|Dingolfing|('bmw',)|vehicle</t>
+          <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>('DE', 'Dingolfing', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1232,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1251,11 +1241,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>41535</v>
+        <v>45355</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1301,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_160000.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1323,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1337,7 +1327,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>160000</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,11 +1336,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45355</v>
+        <v>42185</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1364,25 +1354,29 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Upper Bavaria</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Leipzig</t>
+          <t>Munich, Urban District</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>51.33962</v>
+        <v>48.13743</v>
       </c>
       <c r="P10" t="n">
-        <v>12.37129</v>
+        <v>11.57549</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1391,22 +1385,22 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
+          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_40000.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>DE|Leipzig|('bmw',)|vehicle</t>
+          <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1431,9 +1425,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>40000</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>operational</t>
@@ -1441,11 +1433,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>42185</v>
+        <v>44491</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1495,7 +1487,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1517,12 +1509,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1530,7 +1522,9 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>160000</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>operational</t>
@@ -1542,7 +1536,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44491</v>
+        <v>44876</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1556,29 +1550,29 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Upper Palatinate</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Munich, Urban District</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>48.13743</v>
+        <v>49.01513</v>
       </c>
       <c r="P12" t="n">
-        <v>11.57549</v>
+        <v>12.10161</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1587,22 +1581,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
+          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_160000.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>DE|Munich|('bmw',)|vehicle</t>
+          <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1622,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>160000</v>
+        <v>240000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1635,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>44876</v>
+        <v>45744</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1691,7 +1685,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_240000.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1713,21 +1707,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>240000</v>
+        <v>80000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1740,7 +1734,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45744</v>
+        <v>45657</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1754,29 +1748,25 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Upper Palatinate</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
+          <t>Oxford</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>49.01513</v>
+        <v>51.73213</v>
       </c>
       <c r="P14" t="n">
-        <v>12.10161</v>
+        <v>-1.20631</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1785,22 +1775,22 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
+          <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_240000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_1fba0998-ffe7-54f5-a236-919e234e7829_80000.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>DE|Regensburg|('bmw',)|vehicle</t>
+          <t>GB|Oxfordshire|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1802,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1826,7 +1816,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1835,11 +1825,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>43655</v>
+        <v>45291</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1851,28 +1841,12 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Oxford</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>51.73213</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-1.20631</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -1880,61 +1854,59 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
+          <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1fba0998-ffe7-54f5-a236-919e234e7829_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_0.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('bmw',)|vehicle</t>
+          <t>GB|None|('bmw',)|vehicle</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
+          <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>goodwood</t>
+          <t>allone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>goodwood</t>
+          <t>allone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45291</v>
+        <v>43440</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1959,59 +1931,61 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
+          <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>GB|None|('bmw',)|vehicle</t>
+          <t>FR|None|('byd',)|vehicle</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
+          <t>('FR', 'None', "('byd',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>komárom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>komárom</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>44249</v>
+        <v>42855</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2025,29 +1999,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Cherwell District</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Bicester</t>
-        </is>
-      </c>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>51.89998</v>
+        <v>47.74318</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.15357</v>
+        <v>18.11913</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2056,61 +2018,61 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
+          <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_87ed39d0-95e7-55f0-9c84-367ea52968ab_0.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('arrival',)|vehicle</t>
+          <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
+          <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>cologne</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>cologne</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>80000</v>
+        <v>360000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>43252</v>
+        <v>45447</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2124,25 +2086,29 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
+          <t>Cologne</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Bruxelles-Capitale</t>
+          <t>Cologne District</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>Cologne, Urban District</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Cologne</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>50.85045</v>
+        <v>50.93333</v>
       </c>
       <c r="P18" t="n">
-        <v>4.34878</v>
+        <v>6.95</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2151,48 +2117,48 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
+          <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_d005f306-6f24-5243-9c14-757b40e8e259_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_0ec09a24-125b-5eee-a2c2-db6f7c89e362_360000.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
+          <t>DE|Cologne|('ford',)|vehicle</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>hyundai</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2205,7 +2171,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45292</v>
+        <v>43891</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2219,29 +2185,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Nošovice</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Okres Frýdek-Místek</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Ingolstadt</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Ingolstadt</t>
-        </is>
-      </c>
+          <t>Nošovice</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>48.76508</v>
+        <v>49.66073</v>
       </c>
       <c r="P19" t="n">
-        <v>11.42372</v>
+        <v>18.42633</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2250,48 +2212,48 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
+          <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_120000.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>DE|Ingolstadt|('audi',)|vehicle</t>
+          <t>CZ|Nošovice|('hyundai',)|vehicle</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
+          <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>kia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2300,11 +2262,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>43983</v>
+        <v>45657</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2318,29 +2280,25 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Žilina Region</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Regierungsbezirk Stuttgart</t>
+          <t>Žilina District</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Landkreis Heilbronn</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Neckarsulm</t>
-        </is>
-      </c>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>49.18912</v>
+        <v>49.22315</v>
       </c>
       <c r="P20" t="n">
-        <v>9.22527</v>
+        <v>18.73941</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2349,50 +2307,52 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
+          <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_8c10f625-fea2-51ad-a118-adb9ac7fbea1_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_60000.0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>DE|Neckarsulm|('audi',)|vehicle</t>
+          <t>SK|Žilina Region|('kia',)|vehicle</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
+          <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>40000</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2401,7 +2361,7 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>43440</v>
+        <v>42005</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2413,12 +2373,28 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Bremen</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>53.07582</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8.807169999999999</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2426,44 +2402,44 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
+          <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_303ad2bc-a853-55e8-9566-858510f8d770_40000.0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>FR|None|('byd',)|vehicle</t>
+          <t>DE|Bremen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('byd',)", 'vehicle')</t>
+          <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2476,11 +2452,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>42855</v>
+        <v>43831</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2492,20 +2468,12 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Komárom-Esztergom</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>47.74318</v>
-      </c>
-      <c r="P22" t="n">
-        <v>18.11913</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2513,39 +2481,39 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
+          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_87ed39d0-95e7-55f0-9c84-367ea52968ab_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_0.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
+          <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
+          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2553,9 +2521,7 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>360000</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>operational</t>
@@ -2563,11 +2529,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45447</v>
+        <v>45261</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2579,32 +2545,12 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Cologne District</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Cologne, Urban District</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>50.93333</v>
-      </c>
-      <c r="P23" t="n">
-        <v>6.95</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2612,44 +2558,44 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
+          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0ec09a24-125b-5eee-a2c2-db6f7c89e362_360000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>DE|Cologne|('ford',)|vehicle</t>
+          <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
+          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hyundai</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2666,7 +2612,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>43891</v>
+        <v>43102</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2680,25 +2626,29 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Nošovice</t>
+          <t>Rastatt</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Okres Frýdek-Místek</t>
+          <t>Karlsruhe Region</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Nošovice</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Landkreis Rastatt</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Rastatt</t>
+        </is>
+      </c>
       <c r="O24" t="n">
-        <v>49.66073</v>
+        <v>48.85851</v>
       </c>
       <c r="P24" t="n">
-        <v>18.42633</v>
+        <v>8.20965</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2707,48 +2657,48 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
+          <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_728fcd34-e11b-59cc-ac72-f6f4bfd53540_120000.0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>CZ|Nošovice|('hyundai',)|vehicle</t>
+          <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
+          <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kia</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2761,7 +2711,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>43831</v>
+        <v>42370</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2775,25 +2725,29 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Žilina Region</t>
+          <t>Sindelfingen</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Žilina District</t>
+          <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Žilina</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>Landkreis Böblingen</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Sindelfingen</t>
+        </is>
+      </c>
       <c r="O25" t="n">
-        <v>49.22315</v>
+        <v>48.7</v>
       </c>
       <c r="P25" t="n">
-        <v>18.73941</v>
+        <v>9.01667</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2802,22 +2756,22 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
+          <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_1a71a177-e936-50c5-9103-940e7397cc66_80000.0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>SK|Žilina Region|('kia',)|vehicle</t>
+          <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
+          <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2829,21 +2783,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>vitoria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>vitoria</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2856,7 +2810,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>42005</v>
+        <v>43617</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2868,28 +2822,12 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Bremen</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Kreisfreie Stadt Bremen</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Bremen</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>53.07582</v>
-      </c>
-      <c r="P26" t="n">
-        <v>8.807169999999999</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2897,22 +2835,22 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
+          <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_303ad2bc-a853-55e8-9566-858510f8d770_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_c1ab1fd2-af88-5319-8d29-f5f844946c36_20000.0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>DE|Bremen|('mercedes benz',)|vehicle</t>
+          <t>ES|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2924,21 +2862,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2951,7 +2889,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>43831</v>
+        <v>44530</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2963,12 +2901,20 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bács-Kiskun</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>46.90618</v>
+      </c>
+      <c r="P27" t="n">
+        <v>19.69128</v>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2976,47 +2922,49 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>792aa593-f545-506e-876a-c8156d0c4131</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_792aa593-f545-506e-876a-c8156d0c4131_80000.0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>60000</v>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3024,11 +2972,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45261</v>
+        <v>41275</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3040,12 +2988,24 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>54.90465</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.38222</v>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -3053,48 +3013,48 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_f119dc73-a41d-541d-96ec-a7f18a74dcab_60000.0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>GB|Sunderland|('nissan',)|vehicle</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3103,11 +3063,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>43102</v>
+        <v>45657</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3121,29 +3081,29 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Rastatt</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Karlsruhe Region</t>
+          <t>North</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Landkreis Rastatt</t>
+          <t>Arrondissement of Avesnes-sur-Helpe</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Rastatt</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>48.85851</v>
+        <v>50.27875</v>
       </c>
       <c r="P29" t="n">
-        <v>8.20965</v>
+        <v>3.97267</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -3152,48 +3112,48 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
+          <t>6630540c-9bc6-541b-a124-85fbb4865ffd</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_728fcd34-e11b-59cc-ac72-f6f4bfd53540_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6630540c-9bc6-541b-a124-85fbb4865ffd_40000.0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
+          <t>FR|Maubeuge|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
+          <t>('FR', 'Maubeuge', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3202,11 +3162,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>42370</v>
+        <v>45657</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3220,29 +3180,29 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Regierungsbezirk Stuttgart</t>
+          <t>Meurthe et Moselle</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Landkreis Böblingen</t>
+          <t>Arrondissement of Briey</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>48.7</v>
+        <v>49.17372</v>
       </c>
       <c r="P30" t="n">
-        <v>9.01667</v>
+        <v>5.96869</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3251,48 +3211,48 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
+          <t>7c1498d5-0289-5c56-a848-588df51f6771</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1a71a177-e936-50c5-9103-940e7397cc66_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7c1498d5-0289-5c56-a848-588df51f6771_0.0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
+          <t>FR|Batilly|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('FR', 'Batilly', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3301,11 +3261,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43617</v>
+        <v>45291</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3317,12 +3277,32 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Flins-sur-Seine</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Yvelines</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Arrondissement of Mantes-la-Jolie</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Flins-sur-Seine</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>48.96523</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.87314</v>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -3330,48 +3310,48 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
+          <t>efa6f6c1-a5b5-5aad-bffe-b3e85d787636</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_c1ab1fd2-af88-5319-8d29-f5f844946c36_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_efa6f6c1-a5b5-5aad-bffe-b3e85d787636_40000.0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>ES|None|('mercedes benz',)|vehicle</t>
+          <t>FR|Flins-sur-Seine|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3380,11 +3360,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44530</v>
+        <v>45657</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3398,17 +3378,29 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Bács-Kiskun</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Sandouville</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Seine-Maritime</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Arrondissement of Le Havre</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Sandouville</t>
+        </is>
+      </c>
       <c r="O32" t="n">
-        <v>46.90618</v>
+        <v>49.4978</v>
       </c>
       <c r="P32" t="n">
-        <v>19.69128</v>
+        <v>0.31748</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3417,48 +3409,48 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>792aa593-f545-506e-876a-c8156d0c4131</t>
+          <t>fce8c5b2-5e51-5d37-85d6-3ceea490a597</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_792aa593-f545-506e-876a-c8156d0c4131_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_fce8c5b2-5e51-5d37-85d6-3ceea490a597_0.0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
+          <t>FR|Sandouville|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
+          <t>('FR', 'Sandouville', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3471,7 +3463,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>41275</v>
+        <v>45657</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3485,21 +3477,29 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Arrondissement of Douai</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Douai</t>
+        </is>
+      </c>
       <c r="O33" t="n">
-        <v>54.90465</v>
+        <v>50.37069</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.38222</v>
+        <v>3.07922</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3508,22 +3508,22 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
+          <t>f8b79f53-25f2-516c-8983-966d79119fdc</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f119dc73-a41d-541d-96ec-a7f18a74dcab_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f8b79f53-25f2-516c-8983-966d79119fdc_120000.0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>GB|Sunderland|('nissan',)|vehicle</t>
+          <t>FR|Douai|('renault',)|vehicle</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
+          <t>('FR', 'Douai', "('renault',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3902,39 +3902,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>srellantis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43831</v>
+        <v>45291</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3948,25 +3948,29 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>Poissy</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Yvelines</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Wartburgkreis</t>
+          <t>Arrondissement of Saint-Germain-en-Laye</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Poissy</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>50.9807</v>
+        <v>48.92902</v>
       </c>
       <c r="P38" t="n">
-        <v>10.31522</v>
+        <v>2.04952</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3975,22 +3979,22 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
+          <t>f0462b5a-ae72-5815-9d01-c0d999befd85</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f0462b5a-ae72-5815-9d01-c0d999befd85_40000.0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>DE|Eisenach|('stellantis',)|vehicle</t>
+          <t>FR|Poissy|('srellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Poissy', "('srellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4019,9 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4023,11 +4029,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45536</v>
+        <v>43831</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4073,7 +4079,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_0.0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4095,34 +4101,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>80000</v>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43559</v>
+        <v>45536</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4136,25 +4140,25 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Trnava District</t>
-        </is>
-      </c>
+          <t>Eisenach</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Trnava</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>Wartburgkreis</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
       <c r="O40" t="n">
-        <v>48.37741</v>
+        <v>50.9807</v>
       </c>
       <c r="P40" t="n">
-        <v>17.58723</v>
+        <v>10.31522</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -4163,22 +4167,22 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
+          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
+          <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
+          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4203,19 +4207,21 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>80000</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45108</v>
+        <v>43559</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4261,7 +4267,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_80000.0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4283,34 +4289,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>41061</v>
+        <v>45108</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4324,25 +4328,25 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Trnava District</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Trnava</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>42.23282</v>
+        <v>48.37741</v>
       </c>
       <c r="P42" t="n">
-        <v>-8.72264</v>
+        <v>17.58723</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -4351,22 +4355,22 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
+          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>ES|Galicia|('stellantis',)|vehicle</t>
+          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
+          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4395,9 @@
           <t>ES</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4399,11 +4405,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>44502</v>
+        <v>41061</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4449,7 +4455,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_0.0</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4471,22 +4477,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mulhouse</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mulhouse</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>60000</v>
-      </c>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4494,11 +4498,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45291</v>
+        <v>44502</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4512,29 +4516,25 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Mulhouse</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Haut-Rhin</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Arrondissement of Mulhouse</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>47.75205</v>
+        <v>42.23282</v>
       </c>
       <c r="P44" t="n">
-        <v>7.32866</v>
+        <v>-8.72264</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4543,22 +4543,22 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>f04e6321-7663-5242-a582-e78bf30492fb</t>
+          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f04e6321-7663-5242-a582-e78bf30492fb_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>FR|Mulhouse|('stellantis',)|vehicle</t>
+          <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>('FR', 'Mulhouse', "('stellantis',)", 'vehicle')</t>
+          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4570,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>mulhouse</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>mulhouse</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4584,11 +4584,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4611,29 +4611,29 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Mulhouse</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ille-et-Vilaine</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Arrondissement of Rennes</t>
+          <t>Arrondissement of Mulhouse</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Mulhouse</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>48.11198</v>
+        <v>47.75205</v>
       </c>
       <c r="P45" t="n">
-        <v>-1.67429</v>
+        <v>7.32866</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0f1addfd-3731-5deb-905c-c1ca76aa8f8b</t>
+          <t>f04e6321-7663-5242-a582-e78bf30492fb</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0f1addfd-3731-5deb-905c-c1ca76aa8f8b_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f04e6321-7663-5242-a582-e78bf30492fb_60000.0</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>FR|Rennes|('stellantis',)|vehicle</t>
+          <t>FR|Mulhouse|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>('FR', 'Rennes', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Mulhouse', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sochaux</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sochaux</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4683,20 +4683,20 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4710,29 +4710,29 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Doubs</t>
+          <t>Ille-et-Vilaine</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Arrondissement of Montbéliard</t>
+          <t>Arrondissement of Rennes</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>47.50808</v>
+        <v>48.11198</v>
       </c>
       <c r="P46" t="n">
-        <v>6.82748</v>
+        <v>-1.67429</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4741,39 +4741,39 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>69c19e84-42f0-5366-8453-cb02017d6f48</t>
+          <t>0f1addfd-3731-5deb-905c-c1ca76aa8f8b</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_69c19e84-42f0-5366-8453-cb02017d6f48_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_0f1addfd-3731-5deb-905c-c1ca76aa8f8b_20000.0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>FR|Sochaux|('stellantis',)|vehicle</t>
+          <t>FR|Rennes|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>('FR', 'Sochaux', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Rennes', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stellantis (fiat chrysler)</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hordain</t>
+          <t>sochaux</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>hordain</t>
+          <t>sochaux</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -4809,29 +4809,29 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Hordain</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Doubs</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Arrondissement of Valenciennes</t>
+          <t>Arrondissement of Montbéliard</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Hordain</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>50.26306</v>
+        <v>47.50808</v>
       </c>
       <c r="P47" t="n">
-        <v>3.31358</v>
+        <v>6.82748</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4840,39 +4840,39 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>6cf38a0c-36de-551b-9bcc-3cca04da0224</t>
+          <t>69c19e84-42f0-5366-8453-cb02017d6f48</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6cf38a0c-36de-551b-9bcc-3cca04da0224_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_69c19e84-42f0-5366-8453-cb02017d6f48_40000.0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>FR|Hordain|('stellantis (fiat chrysler)',)|vehicle</t>
+          <t>FR|Sochaux|('stellantis',)|vehicle</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>('FR', 'Hordain', "('stellantis (fiat chrysler)',)", 'vehicle')</t>
+          <t>('FR', 'Sochaux', "('stellantis',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>srellantis</t>
+          <t>stellantis (fiat chrysler)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>hordain</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>hordain</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4908,29 +4908,29 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Poissy</t>
+          <t>Hordain</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>North</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Arrondissement of Saint-Germain-en-Laye</t>
+          <t>Arrondissement of Valenciennes</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Poissy</t>
+          <t>Hordain</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>48.92902</v>
+        <v>50.26306</v>
       </c>
       <c r="P48" t="n">
-        <v>2.04952</v>
+        <v>3.31358</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4939,48 +4939,48 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>f0462b5a-ae72-5815-9d01-c0d999befd85</t>
+          <t>6cf38a0c-36de-551b-9bcc-3cca04da0224</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f0462b5a-ae72-5815-9d01-c0d999befd85_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6cf38a0c-36de-551b-9bcc-3cca04da0224_40000.0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>FR|Poissy|('srellantis',)|vehicle</t>
+          <t>FR|Hordain|('stellantis (fiat chrysler)',)|vehicle</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>('FR', 'Poissy', "('srellantis',)", 'vehicle')</t>
+          <t>('FR', 'Hordain', "('stellantis (fiat chrysler)',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>tata jlr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>320000</v>
+        <v>20000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44642</v>
+        <v>43101</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5007,25 +5007,25 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>Knowsley</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Knowsley</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Berlin, Stadt</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
+          <t>Halewood</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>52.52437</v>
+        <v>53.36434</v>
       </c>
       <c r="P49" t="n">
-        <v>13.41053</v>
+        <v>-2.82053</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5034,22 +5034,22 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
+          <t>e2b88591-16ed-593d-81d0-f4437853d855</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ab942289-b19a-5128-8112-1c5a42e60372_320000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_e2b88591-16ed-593d-81d0-f4437853d855_20000.0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>DE|Berlin|('tesla',)|vehicle</t>
+          <t>GB|Knowsley|('tata jlr',)|vehicle</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
+          <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5061,23 +5061,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>berlin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>berlin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>320000</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5086,7 +5088,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42157</v>
+        <v>44642</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5100,21 +5102,25 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tilburg Municipality</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Tilburg Municipality</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Berlin, Stadt</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
       <c r="O50" t="n">
-        <v>51.55551</v>
+        <v>52.52437</v>
       </c>
       <c r="P50" t="n">
-        <v>5.0913</v>
+        <v>13.41053</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5123,52 +5129,50 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
+          <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_ab942289-b19a-5128-8112-1c5a42e60372_320000.0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
+          <t>DE|Berlin|('tesla',)|vehicle</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
+          <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>tilburg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>tilburg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>140000</v>
-      </c>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5177,7 +5181,7 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>41426</v>
+        <v>42157</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5191,17 +5195,21 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>Tilburg Municipality</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Tilburg Municipality</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>48.14816</v>
+        <v>51.55551</v>
       </c>
       <c r="P51" t="n">
-        <v>17.10674</v>
+        <v>5.0913</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5210,22 +5218,22 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
+          <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_24f54170-5f2a-500a-8994-da2daf36ed6a_140000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
+          <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
+          <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5237,21 +5245,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>500000</v>
+        <v>140000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5260,11 +5268,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43773</v>
+        <v>41426</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5278,25 +5286,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Zwickau</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Zwickau</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Zwickau</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>50.72724</v>
+        <v>48.14816</v>
       </c>
       <c r="P52" t="n">
-        <v>12.48839</v>
+        <v>17.10674</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5305,47 +5305,49 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
+          <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5407b64f-8759-5926-9898-d6b7600bdfe1_500000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_24f54170-5f2a-500a-8994-da2daf36ed6a_140000.0</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>DE|Zwickau|('volkswagen',)|vehicle</t>
+          <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>volvo group</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>blainville</t>
+          <t>zwickau</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>blainville</t>
+          <t>zwickau</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>500000</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>operational</t>
@@ -5353,11 +5355,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43646</v>
+        <v>43773</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5369,12 +5371,28 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>50.72724</v>
+      </c>
+      <c r="P53" t="n">
+        <v>12.48839</v>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -5382,59 +5400,61 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
+          <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_5407b64f-8759-5926-9898-d6b7600bdfe1_500000.0</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>FR|None|('volvo group',)|vehicle</t>
+          <t>DE|Zwickau|('volkswagen',)|vehicle</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
+          <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>volvo group</t>
+          <t>volvo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>120000</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45183</v>
+        <v>45717</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5448,29 +5468,25 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Västra Götaland</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>East Flanders Province</t>
+          <t>Gothenburg Municipality</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
+          <t>Torslanda</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>51.05</v>
+        <v>57.72504</v>
       </c>
       <c r="P54" t="n">
-        <v>3.71667</v>
+        <v>11.76903</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5479,22 +5495,22 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>43827abe-ea8c-5a39-87d9-c1114db92c51</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_43827abe-ea8c-5a39-87d9-c1114db92c51_120000.0</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>SE|Västra Götaland|('volvo',)|vehicle</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5506,32 +5522,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>blainville</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>blainville</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45777</v>
+        <v>43646</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5543,32 +5559,12 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>East Flanders Province</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="O55" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="P55" t="n">
-        <v>3.71667</v>
-      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -5576,61 +5572,59 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>FR|None|('volvo group',)|vehicle</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>volvo</t>
+          <t>volvo group</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>120000</v>
-      </c>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45717</v>
+        <v>45183</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5644,25 +5638,29 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Västra Götaland</t>
+          <t>Arrondissement of Ghent</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>East Flanders Province</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Torslanda</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
       <c r="O56" t="n">
-        <v>57.72504</v>
+        <v>51.05</v>
       </c>
       <c r="P56" t="n">
-        <v>11.76903</v>
+        <v>3.71667</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -5671,61 +5669,59 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>43827abe-ea8c-5a39-87d9-c1114db92c51</t>
+          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_43827abe-ea8c-5a39-87d9-c1114db92c51_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>SE|Västra Götaland|('volvo',)|vehicle</t>
+          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tata jlr</t>
+          <t>volvo group</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>20000</v>
-      </c>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43101</v>
+        <v>45777</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5739,25 +5735,29 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Arrondissement of Ghent</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>East Flanders Province</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Halewood</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
       <c r="O57" t="n">
-        <v>53.36434</v>
+        <v>51.05</v>
       </c>
       <c r="P57" t="n">
-        <v>-2.82053</v>
+        <v>3.71667</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5766,22 +5766,22 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>e2b88591-16ed-593d-81d0-f4437853d855</t>
+          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_e2b88591-16ed-593d-81d0-f4437853d855_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>GB|Knowsley|('tata jlr',)|vehicle</t>
+          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>
       </c>
     </row>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,55 +485,60 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>admin_group_key</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>adm1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>adm2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>adm3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>adm4</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>lon</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>project_id</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>capacity_id</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>project_key_str</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>project_key_tuple</t>
         </is>
@@ -596,41 +601,46 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Cherwell District</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Bicester</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>51.89998</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>-1.15357</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>GB|Oxfordshire|('arrival',)|vehicle</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
         </is>
@@ -688,36 +698,41 @@
           <t>Győr-Moson-Sopron</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Győr-Moson-Sopron</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>47.68333</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>17.63512</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>696036ed-ca14-5c3f-87d3-afbe17e5e286</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_696036ed-ca14-5c3f-87d3-afbe17e5e286_40000.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>HU|Győr-Moson-Sopron|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>('HU', 'Győr-Moson-Sopron', "('audi',)", 'vehicle')</t>
         </is>
@@ -777,42 +792,47 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Bruxelles-Capitale</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Arrondissement Brussel-Hoofdstad</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>50.85045</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>4.34878</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_d005f306-6f24-5243-9c14-757b40e8e259_80000.0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
         </is>
@@ -872,46 +892,51 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Upper Bavaria</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Kreisfreie Stadt Ingolstadt</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Ingolstadt</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>48.76508</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>11.42372</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_20000.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>DE|Ingolstadt|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
         </is>
@@ -971,46 +996,51 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Neckarsulm</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Landkreis Heilbronn</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Neckarsulm</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>49.18912</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>9.22527</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_8c10f625-fea2-51ad-a118-adb9ac7fbea1_40000.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>DE|Neckarsulm|('audi',)|vehicle</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
         </is>
@@ -1070,46 +1100,51 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Dingolfing</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Lower Bavaria</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Landkreis Dingolfing-Landau</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Dingolfing</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>48.64244</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>12.49283</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>daf49ae1-44a2-5e11-a257-ab0a1d11d24b</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_daf49ae1-44a2-5e11-a257-ab0a1d11d24b_180000.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>DE|Dingolfing|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>('DE', 'Dingolfing', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1167,44 +1202,49 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>51.33962</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>12.37129</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_40000.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1262,44 +1302,49 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>51.33962</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>12.37129</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_160000.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>DE|Leipzig|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1359,46 +1404,51 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>Upper Bavaria</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Munich, Urban District</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>48.13743</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>11.57549</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_40000.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1456,46 +1506,51 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Upper Bavaria</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Munich, Urban District</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>48.13743</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>11.57549</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>DE|Munich|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1555,46 +1610,51 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>Upper Palatinate</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>49.01513</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>12.10161</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_160000.0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1654,46 +1714,51 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>Upper Palatinate</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>49.01513</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>12.10161</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_240000.0</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>DE|Regensburg|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1758,37 +1823,42 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>Oxford</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>51.73213</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>-1.20631</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_1fba0998-ffe7-54f5-a236-919e234e7829_80000.0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>GB|Oxfordshire|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1847,27 +1917,28 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_0.0</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>GB|None|('bmw',)|vehicle</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
         </is>
@@ -1924,27 +1995,28 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>FR|None|('byd',)|vehicle</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>('FR', 'None', "('byd',)", 'vehicle')</t>
         </is>
@@ -2002,36 +2074,41 @@
           <t>Komárom-Esztergom</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>47.74318</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>18.11913</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_87ed39d0-95e7-55f0-9c84-367ea52968ab_0.0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
         </is>
@@ -2091,46 +2168,51 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Cologne</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>Cologne District</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Cologne, Urban District</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Cologne</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>50.93333</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>6.95</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_0ec09a24-125b-5eee-a2c2-db6f7c89e362_360000.0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>DE|Cologne|('ford',)|vehicle</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
         </is>
@@ -2190,42 +2272,47 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Nošovice</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>Okres Frýdek-Místek</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Nošovice</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>49.66073</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>18.42633</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_120000.0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>CZ|Nošovice|('hyundai',)|vehicle</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
         </is>
@@ -2285,42 +2372,47 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Žilina Region</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>Žilina District</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Žilina</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>49.22315</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>18.73941</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_60000.0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>SK|Žilina Region|('kia',)|vehicle</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
         </is>
@@ -2378,44 +2470,49 @@
           <t>Bremen</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bremen</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Kreisfreie Stadt Bremen</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Bremen</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>53.07582</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>8.807169999999999</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_303ad2bc-a853-55e8-9566-858510f8d770_40000.0</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>DE|Bremen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2474,27 +2571,28 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_0.0</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2551,27 +2649,28 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>DE|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2631,46 +2730,51 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Rastatt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>Karlsruhe Region</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Landkreis Rastatt</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Rastatt</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>48.85851</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>8.20965</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_728fcd34-e11b-59cc-ac72-f6f4bfd53540_120000.0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2730,46 +2834,51 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Sindelfingen</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Landkreis Böblingen</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sindelfingen</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>9.01667</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_1a71a177-e936-50c5-9103-940e7397cc66_80000.0</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2828,27 +2937,28 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_c1ab1fd2-af88-5319-8d29-f5f844946c36_20000.0</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>ES|None|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2906,36 +3016,41 @@
           <t>Bács-Kiskun</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bács-Kiskun</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>46.90618</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>19.69128</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>792aa593-f545-506e-876a-c8156d0c4131</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_792aa593-f545-506e-876a-c8156d0c4131_80000.0</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
         </is>
@@ -2998,35 +3113,40 @@
           <t>Sunderland</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>54.90465</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>-1.38222</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f119dc73-a41d-541d-96ec-a7f18a74dcab_60000.0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>GB|Sunderland|('nissan',)|vehicle</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
         </is>
@@ -3086,46 +3206,51 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>Maubeuge</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>North</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Arrondissement of Avesnes-sur-Helpe</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Maubeuge</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>50.27875</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.97267</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>6630540c-9bc6-541b-a124-85fbb4865ffd</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_6630540c-9bc6-541b-a124-85fbb4865ffd_40000.0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>FR|Maubeuge|('renault',)|vehicle</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>('FR', 'Maubeuge', "('renault',)", 'vehicle')</t>
         </is>
@@ -3185,46 +3310,51 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Batilly</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Meurthe et Moselle</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Arrondissement of Briey</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Batilly</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>49.17372</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>5.96869</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>7c1498d5-0289-5c56-a848-588df51f6771</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_7c1498d5-0289-5c56-a848-588df51f6771_0.0</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>FR|Batilly|('renault',)|vehicle</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>('FR', 'Batilly', "('renault',)", 'vehicle')</t>
         </is>
@@ -3284,46 +3414,51 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Flins-sur-Seine</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>Yvelines</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Arrondissement of Mantes-la-Jolie</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Flins-sur-Seine</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>48.96523</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1.87314</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>efa6f6c1-a5b5-5aad-bffe-b3e85d787636</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_efa6f6c1-a5b5-5aad-bffe-b3e85d787636_40000.0</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>FR|Flins-sur-Seine|('renault',)|vehicle</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>('FR', 'Flins-sur-Seine', "('renault',)", 'vehicle')</t>
         </is>
@@ -3383,46 +3518,51 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Sandouville</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>Seine-Maritime</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Arrondissement of Le Havre</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sandouville</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>49.4978</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>0.31748</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>fce8c5b2-5e51-5d37-85d6-3ceea490a597</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_fce8c5b2-5e51-5d37-85d6-3ceea490a597_0.0</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>FR|Sandouville|('renault',)|vehicle</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>('FR', 'Sandouville', "('renault',)", 'vehicle')</t>
         </is>
@@ -3482,46 +3622,51 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Douai</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>North</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Arrondissement of Douai</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Douai</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>50.37069</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.07922</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>f8b79f53-25f2-516c-8983-966d79119fdc</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f8b79f53-25f2-516c-8983-966d79119fdc_120000.0</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>FR|Douai|('renault',)|vehicle</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>('FR', 'Douai', "('renault',)", 'vehicle')</t>
         </is>
@@ -3579,38 +3724,43 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Krapina-Zagorje</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>Municipality of Veliko Trgovišće</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>46</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>15.85</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>916f228d-de7f-5acb-9645-66e4b8495022</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_916f228d-de7f-5acb-9645-66e4b8495022_nan</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>HR|Krapina-Zagorje|('rimac automobili',)|vehicle</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>('HR', 'Krapina-Zagorje', "('rimac automobili',)", 'vehicle')</t>
         </is>
@@ -3670,42 +3820,47 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Catalonia</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Martorell</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>41.47402</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>1.93062</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>f2de5535-0d2e-5fe4-971b-d70bcab45f62</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f2de5535-0d2e-5fe4-971b-d70bcab45f62_40000.0</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>ES|Catalonia|('seat',)|vehicle</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>('ES', 'Catalonia', "('seat',)", 'vehicle')</t>
         </is>
@@ -3765,42 +3920,47 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>Mladá Boleslav District</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Mladá Boleslav</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>50.41135</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>14.90318</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_120000.0</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
@@ -3858,42 +4018,47 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>Mladá Boleslav District</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Mladá Boleslav</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>50.41135</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>14.90318</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_nan</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
         </is>
@@ -3953,46 +4118,51 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Poissy</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>Yvelines</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Arrondissement of Saint-Germain-en-Laye</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Poissy</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>48.92902</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>2.04952</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>f0462b5a-ae72-5815-9d01-c0d999befd85</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f0462b5a-ae72-5815-9d01-c0d999befd85_40000.0</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>FR|Poissy|('srellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>('FR', 'Poissy', "('srellantis',)", 'vehicle')</t>
         </is>
@@ -4050,44 +4220,49 @@
           <t>Eisenach</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Wartburgkreis</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Eisenach</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>50.9807</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>10.31522</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_0.0</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4143,44 +4318,49 @@
           <t>Eisenach</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>Wartburgkreis</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Eisenach</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>50.9807</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>10.31522</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>DE|Eisenach|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4240,42 +4420,47 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>Trnava District</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Trnava</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
         <v>48.37741</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>17.58723</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_80000.0</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4333,42 +4518,47 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>Trnava District</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Trnava</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>48.37741</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>17.58723</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>SK|Trnava Region|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4428,42 +4618,47 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>Pontevedra</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Vigo</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
         <v>42.23282</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>-8.72264</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_0.0</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4521,42 +4716,47 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>Pontevedra</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Vigo</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
         <v>42.23282</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>-8.72264</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>ES|Galicia|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4616,46 +4816,51 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>Haut-Rhin</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Arrondissement of Mulhouse</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Mulhouse</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>47.75205</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>7.32866</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>f04e6321-7663-5242-a582-e78bf30492fb</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_f04e6321-7663-5242-a582-e78bf30492fb_60000.0</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>FR|Mulhouse|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>('FR', 'Mulhouse', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4715,46 +4920,51 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>Ille-et-Vilaine</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Arrondissement of Rennes</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>48.11198</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>-1.67429</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>0f1addfd-3731-5deb-905c-c1ca76aa8f8b</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_0f1addfd-3731-5deb-905c-c1ca76aa8f8b_20000.0</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>FR|Rennes|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>('FR', 'Rennes', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4814,46 +5024,51 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
           <t>Doubs</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Arrondissement of Montbéliard</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Sochaux</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>47.50808</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>6.82748</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>69c19e84-42f0-5366-8453-cb02017d6f48</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_69c19e84-42f0-5366-8453-cb02017d6f48_40000.0</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>FR|Sochaux|('stellantis',)|vehicle</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>('FR', 'Sochaux', "('stellantis',)", 'vehicle')</t>
         </is>
@@ -4913,46 +5128,51 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>Hordain</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
           <t>North</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Arrondissement of Valenciennes</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Hordain</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>50.26306</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>3.31358</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>6cf38a0c-36de-551b-9bcc-3cca04da0224</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_6cf38a0c-36de-551b-9bcc-3cca04da0224_40000.0</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>FR|Hordain|('stellantis (fiat chrysler)',)|vehicle</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>('FR', 'Hordain', "('stellantis (fiat chrysler)',)", 'vehicle')</t>
         </is>
@@ -5017,37 +5237,42 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>Knowsley</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>Halewood</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
         <v>53.36434</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>-2.82053</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>e2b88591-16ed-593d-81d0-f4437853d855</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_e2b88591-16ed-593d-81d0-f4437853d855_20000.0</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>GB|Knowsley|('tata jlr',)|vehicle</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
         </is>
@@ -5105,44 +5330,49 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>Berlin, Stadt</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>52.52437</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>13.41053</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_ab942289-b19a-5128-8112-1c5a42e60372_320000.0</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>DE|Berlin|('tesla',)|vehicle</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
         </is>
@@ -5203,35 +5433,40 @@
           <t>Tilburg Municipality</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Tilburg Municipality</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
         <v>51.55551</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>5.0913</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
         </is>
@@ -5289,36 +5524,41 @@
           <t>Bratislava Region</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
         <v>48.14816</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>17.10674</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_24f54170-5f2a-500a-8994-da2daf36ed6a_140000.0</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
         </is>
@@ -5376,44 +5616,49 @@
           <t>Zwickau</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Zwickau</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Zwickau</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Zwickau</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
         <v>50.72724</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>12.48839</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_5407b64f-8759-5926-9898-d6b7600bdfe1_500000.0</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>DE|Zwickau|('volkswagen',)|vehicle</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
         </is>
@@ -5445,7 +5690,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5454,7 +5699,7 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45717</v>
+        <v>45657</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5468,7 +5713,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Västra Götaland</t>
+          <t>Gothenburg Municipality</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5478,39 +5723,44 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>Gothenburg Municipality</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>Torslanda</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
         <v>57.72504</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>11.76903</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>43827abe-ea8c-5a39-87d9-c1114db92c51</t>
-        </is>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_43827abe-ea8c-5a39-87d9-c1114db92c51_120000.0</t>
+          <t>67f70d66-387d-5b85-b56f-0c54abdc664f</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SE|Västra Götaland|('volvo',)|vehicle</t>
+          <t>68d684fc1c2e9d8ed1487afa_67f70d66-387d-5b85-b56f-0c54abdc664f_120000.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>('SE', 'Västra Götaland', "('volvo',)", 'vehicle')</t>
+          <t>SE|Gothenburg Municipality|('volvo',)|vehicle</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>('SE', 'Gothenburg Municipality', "('volvo',)", 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5565,27 +5815,28 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>FR|None|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
         </is>
@@ -5643,46 +5894,51 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>East Flanders Province</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Arrondissement of Ghent</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Gent</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>51.05</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>3.71667</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>
@@ -5740,46 +5996,51 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>East Flanders Province</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Arrondissement of Ghent</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Gent</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>51.05</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>3.71667</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
         </is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>a6afa10f-a63b-5eac-88f5-91a2fe0c95f2</t>
+          <t>b4377ec9-627e-56d9-8110-ee5e39a6f15b</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_a6afa10f-a63b-5eac-88f5-91a2fe0c95f2_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_b4377ec9-627e-56d9-8110-ee5e39a6f15b_nan</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('arrival',)|vehicle</t>
+          <t>GB|Oxfordshire|arrival|vehicle</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('arrival',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', 'arrival', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>696036ed-ca14-5c3f-87d3-afbe17e5e286</t>
+          <t>33f0261c-2068-58e3-b6de-7de3feedf15d</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_696036ed-ca14-5c3f-87d3-afbe17e5e286_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_33f0261c-2068-58e3-b6de-7de3feedf15d_40000.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HU|Győr-Moson-Sopron|('audi',)|vehicle</t>
+          <t>HU|Győr-Moson-Sopron|audi|vehicle</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>('HU', 'Győr-Moson-Sopron', "('audi',)", 'vehicle')</t>
+          <t>('HU', 'Győr-Moson-Sopron', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>d005f306-6f24-5243-9c14-757b40e8e259</t>
+          <t>72f60389-27c4-5075-b572-b6994992f5f9</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_d005f306-6f24-5243-9c14-757b40e8e259_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_72f60389-27c4-5075-b572-b6994992f5f9_80000.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>BE|Arrondissement Brussel-Hoofdstad|('audi',)|vehicle</t>
+          <t>BE|Arrondissement Brussel-Hoofdstad|audi|vehicle</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement Brussel-Hoofdstad', "('audi',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement Brussel-Hoofdstad', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>f3187b2a-14b8-5526-ac0e-fa9f6dc48897</t>
+          <t>318375f1-8e1f-5e1c-adc8-26827396c806</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f3187b2a-14b8-5526-ac0e-fa9f6dc48897_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_318375f1-8e1f-5e1c-adc8-26827396c806_20000.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>DE|Ingolstadt|('audi',)|vehicle</t>
+          <t>DE|Ingolstadt|audi|vehicle</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>('DE', 'Ingolstadt', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Ingolstadt', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>8c10f625-fea2-51ad-a118-adb9ac7fbea1</t>
+          <t>1751b9ed-efe4-586f-9daa-1865eff86071</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_8c10f625-fea2-51ad-a118-adb9ac7fbea1_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_1751b9ed-efe4-586f-9daa-1865eff86071_40000.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>DE|Neckarsulm|('audi',)|vehicle</t>
+          <t>DE|Neckarsulm|audi|vehicle</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>('DE', 'Neckarsulm', "('audi',)", 'vehicle')</t>
+          <t>('DE', 'Neckarsulm', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Dingolfing</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>daf49ae1-44a2-5e11-a257-ab0a1d11d24b</t>
+          <t>d9373345-9500-5e3a-80b8-7311eaa846b7</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_daf49ae1-44a2-5e11-a257-ab0a1d11d24b_180000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_d9373345-9500-5e3a-80b8-7311eaa846b7_180000.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>DE|Dingolfing|('bmw',)|vehicle</t>
+          <t>DE|Dingolfing|bmw|vehicle</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>('DE', 'Dingolfing', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Dingolfing', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1231,22 +1231,22 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
+          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_40000.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>DE|Leipzig|('bmw',)|vehicle</t>
+          <t>DE|Leipzig|bmw|vehicle</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1331,22 +1331,22 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>9aa81188-d35f-5bf6-b760-44b1f80b4d6c</t>
+          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_9aa81188-d35f-5bf6-b760-44b1f80b4d6c_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_160000.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DE|Leipzig|('bmw',)|vehicle</t>
+          <t>DE|Leipzig|bmw|vehicle</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1435,22 +1435,22 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
+          <t>afda602b-9bd5-55c2-9a85-fe15887ea212</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_afda602b-9bd5-55c2-9a85-fe15887ea212_40000.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>DE|Munich|('bmw',)|vehicle</t>
+          <t>DE|Munich|bmw|vehicle</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Munich', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>655601d6-44d7-5fae-9f00-aed5f36c0462</t>
+          <t>afda602b-9bd5-55c2-9a85-fe15887ea212</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_655601d6-44d7-5fae-9f00-aed5f36c0462_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_afda602b-9bd5-55c2-9a85-fe15887ea212_nan</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>DE|Munich|('bmw',)|vehicle</t>
+          <t>DE|Munich|bmw|vehicle</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Munich', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1641,22 +1641,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
+          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_160000.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>DE|Regensburg|('bmw',)|vehicle</t>
+          <t>DE|Regensburg|bmw|vehicle</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1745,22 +1745,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6d0da839-f19a-5497-8a1f-befe19c9e09b</t>
+          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6d0da839-f19a-5497-8a1f-befe19c9e09b_240000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_240000.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>DE|Regensburg|('bmw',)|vehicle</t>
+          <t>DE|Regensburg|bmw|vehicle</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', "('bmw',)", 'vehicle')</t>
+          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1845,22 +1845,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1fba0998-ffe7-54f5-a236-919e234e7829</t>
+          <t>474ec8c2-c923-55e9-9407-71ce51007407</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1fba0998-ffe7-54f5-a236-919e234e7829_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_474ec8c2-c923-55e9-9407-71ce51007407_80000.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|('bmw',)|vehicle</t>
+          <t>GB|Oxfordshire|bmw|vehicle</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', "('bmw',)", 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1925,22 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>ecd072cf-0eac-532c-9197-9ec57c2ffeb7</t>
+          <t>909df65e-53ad-5d11-983c-19d2a628d5f9</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ecd072cf-0eac-532c-9197-9ec57c2ffeb7_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_909df65e-53ad-5d11-983c-19d2a628d5f9_0.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>GB|None|('bmw',)|vehicle</t>
+          <t>GB|None|bmw|vehicle</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>('GB', 'None', "('bmw',)", 'vehicle')</t>
+          <t>('GB', 'None', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2003,22 +2003,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>22ff6ad3-2641-5943-8217-7da301746c58</t>
+          <t>ff42e3de-ca7c-5924-a756-d05062bfaac4</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_22ff6ad3-2641-5943-8217-7da301746c58_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_ff42e3de-ca7c-5924-a756-d05062bfaac4_nan</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>FR|None|('byd',)|vehicle</t>
+          <t>FR|None|byd|vehicle</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('byd',)", 'vehicle')</t>
+          <t>('FR', 'None', 'byd', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2095,22 +2095,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>87ed39d0-95e7-55f0-9c84-367ea52968ab</t>
+          <t>41140c52-225e-5738-beaa-13145ea3cf59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_87ed39d0-95e7-55f0-9c84-367ea52968ab_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_41140c52-225e-5738-beaa-13145ea3cf59_0.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>HU|Komárom-Esztergom|('byd',)|vehicle</t>
+          <t>HU|Komárom-Esztergom|byd|vehicle</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>('HU', 'Komárom-Esztergom', "('byd',)", 'vehicle')</t>
+          <t>('HU', 'Komárom-Esztergom', 'byd', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2199,22 +2199,22 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0ec09a24-125b-5eee-a2c2-db6f7c89e362</t>
+          <t>b42f04b4-6b19-5f3e-9dbb-b7e98880b5ad</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0ec09a24-125b-5eee-a2c2-db6f7c89e362_360000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_b42f04b4-6b19-5f3e-9dbb-b7e98880b5ad_360000.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>DE|Cologne|('ford',)|vehicle</t>
+          <t>DE|Cologne|ford|vehicle</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>('DE', 'Cologne', "('ford',)", 'vehicle')</t>
+          <t>('DE', 'Cologne', 'ford', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Nošovice</t>
+          <t>Moravskoslezský</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2299,22 +2299,22 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>91c3a3a6-5ae4-5816-bdb3-9af8631e0671</t>
+          <t>60d7afdf-9005-53df-ab21-93ee3d549c47</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_91c3a3a6-5ae4-5816-bdb3-9af8631e0671_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_60d7afdf-9005-53df-ab21-93ee3d549c47_120000.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>CZ|Nošovice|('hyundai',)|vehicle</t>
+          <t>CZ|Nošovice|hyundai|vehicle</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>('CZ', 'Nošovice', "('hyundai',)", 'vehicle')</t>
+          <t>('CZ', 'Nošovice', 'hyundai', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2399,22 +2399,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>7a65fbfe-29d4-5f10-95e3-8cf4634b0088</t>
+          <t>28bf3caf-06c8-5191-98cb-97c7ea26be54</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7a65fbfe-29d4-5f10-95e3-8cf4634b0088_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_28bf3caf-06c8-5191-98cb-97c7ea26be54_60000.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SK|Žilina Region|('kia',)|vehicle</t>
+          <t>SK|Žilina Region|kia|vehicle</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>('SK', 'Žilina Region', "('kia',)", 'vehicle')</t>
+          <t>('SK', 'Žilina Region', 'kia', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>303ad2bc-a853-55e8-9566-858510f8d770</t>
+          <t>a872b950-3bbe-50cf-8d40-35d08fc41ecc</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_303ad2bc-a853-55e8-9566-858510f8d770_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a872b950-3bbe-50cf-8d40-35d08fc41ecc_40000.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>DE|Bremen|('mercedes benz',)|vehicle</t>
+          <t>DE|Bremen|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>('DE', 'Bremen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Bremen', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2579,22 +2579,22 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_0.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>DE|None|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2657,22 +2657,22 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>5adfe1a0-5af6-579e-b8fc-45382ca79c99</t>
+          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5adfe1a0-5af6-579e-b8fc-45382ca79c99_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_nan</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>DE|None|('mercedes benz',)|vehicle</t>
+          <t>DE|None|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>('DE', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Rastatt</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2761,22 +2761,22 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>728fcd34-e11b-59cc-ac72-f6f4bfd53540</t>
+          <t>a138278e-fa43-5700-9479-61f888ac0dde</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_728fcd34-e11b-59cc-ac72-f6f4bfd53540_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a138278e-fa43-5700-9479-61f888ac0dde_120000.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>DE|Rastatt|('mercedes benz',)|vehicle</t>
+          <t>DE|Rastatt|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>('DE', 'Rastatt', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Rastatt', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2865,22 +2865,22 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1a71a177-e936-50c5-9103-940e7397cc66</t>
+          <t>81687d9c-3bf4-5901-9814-be851b7e03d1</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1a71a177-e936-50c5-9103-940e7397cc66_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_81687d9c-3bf4-5901-9814-be851b7e03d1_80000.0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>DE|Sindelfingen|('mercedes benz',)|vehicle</t>
+          <t>DE|Sindelfingen|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>('DE', 'Sindelfingen', "('mercedes benz',)", 'vehicle')</t>
+          <t>('DE', 'Sindelfingen', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2945,22 +2945,22 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>c1ab1fd2-af88-5319-8d29-f5f844946c36</t>
+          <t>6862c608-86bf-5b3c-a51f-b20faa029caa</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_c1ab1fd2-af88-5319-8d29-f5f844946c36_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6862c608-86bf-5b3c-a51f-b20faa029caa_20000.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>ES|None|('mercedes benz',)|vehicle</t>
+          <t>ES|None|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>('ES', 'None', "('mercedes benz',)", 'vehicle')</t>
+          <t>('ES', 'None', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3037,22 +3037,22 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>792aa593-f545-506e-876a-c8156d0c4131</t>
+          <t>0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_792aa593-f545-506e-876a-c8156d0c4131_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2_80000.0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>HU|Bács-Kiskun|('mercedes benz',)|vehicle</t>
+          <t>HU|Bács-Kiskun|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>('HU', 'Bács-Kiskun', "('mercedes benz',)", 'vehicle')</t>
+          <t>('HU', 'Bács-Kiskun', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3133,22 +3133,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>f119dc73-a41d-541d-96ec-a7f18a74dcab</t>
+          <t>5e64d344-4569-5f9e-bf88-fa88fa5f55de</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f119dc73-a41d-541d-96ec-a7f18a74dcab_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5e64d344-4569-5f9e-bf88-fa88fa5f55de_60000.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>GB|Sunderland|('nissan',)|vehicle</t>
+          <t>GB|Sunderland|nissan|vehicle</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>('GB', 'Sunderland', "('nissan',)", 'vehicle')</t>
+          <t>('GB', 'Sunderland', 'nissan', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Maubeuge</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6630540c-9bc6-541b-a124-85fbb4865ffd</t>
+          <t>ae2d47e1-87d3-57a5-a054-c96dec440280</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6630540c-9bc6-541b-a124-85fbb4865ffd_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_40000.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>FR|Maubeuge|('renault',)|vehicle</t>
+          <t>FR|Maubeuge|renault|vehicle</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>('FR', 'Maubeuge', "('renault',)", 'vehicle')</t>
+          <t>('FR', 'Maubeuge', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7c1498d5-0289-5c56-a848-588df51f6771</t>
+          <t>307c4123-5be8-5174-ad9d-1840e75df719</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7c1498d5-0289-5c56-a848-588df51f6771_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_307c4123-5be8-5174-ad9d-1840e75df719_0.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>FR|Batilly|('renault',)|vehicle</t>
+          <t>FR|Batilly|renault|vehicle</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>('FR', 'Batilly', "('renault',)", 'vehicle')</t>
+          <t>('FR', 'Batilly', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Flins-sur-Seine</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>efa6f6c1-a5b5-5aad-bffe-b3e85d787636</t>
+          <t>5140a707-9f43-506f-868e-0bce2129328e</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_efa6f6c1-a5b5-5aad-bffe-b3e85d787636_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_40000.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>FR|Flins-sur-Seine|('renault',)|vehicle</t>
+          <t>FR|Flins-sur-Seine|renault|vehicle</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>('FR', 'Flins-sur-Seine', "('renault',)", 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3549,22 +3549,22 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>fce8c5b2-5e51-5d37-85d6-3ceea490a597</t>
+          <t>424b7ed5-fc12-5e41-b341-a5b1dde327f5</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_fce8c5b2-5e51-5d37-85d6-3ceea490a597_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_424b7ed5-fc12-5e41-b341-a5b1dde327f5_0.0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>FR|Sandouville|('renault',)|vehicle</t>
+          <t>FR|Sandouville|renault|vehicle</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>('FR', 'Sandouville', "('renault',)", 'vehicle')</t>
+          <t>('FR', 'Sandouville', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3653,22 +3653,22 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>f8b79f53-25f2-516c-8983-966d79119fdc</t>
+          <t>252dc9b3-ab0a-55e9-873c-064f96c53ea6</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f8b79f53-25f2-516c-8983-966d79119fdc_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_120000.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>FR|Douai|('renault',)|vehicle</t>
+          <t>FR|Douai|renault|vehicle</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>('FR', 'Douai', "('renault',)", 'vehicle')</t>
+          <t>('FR', 'Douai', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3747,22 +3747,22 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>916f228d-de7f-5acb-9645-66e4b8495022</t>
+          <t>df7be9cf-b360-575d-9cfa-de4b0f37a3a4</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_916f228d-de7f-5acb-9645-66e4b8495022_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_df7be9cf-b360-575d-9cfa-de4b0f37a3a4_nan</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>HR|Krapina-Zagorje|('rimac automobili',)|vehicle</t>
+          <t>HR|Krapina-Zagorje|rimac automobili|vehicle</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>('HR', 'Krapina-Zagorje', "('rimac automobili',)", 'vehicle')</t>
+          <t>('HR', 'Krapina-Zagorje', 'rimac automobili', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3847,22 +3847,22 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>f2de5535-0d2e-5fe4-971b-d70bcab45f62</t>
+          <t>0e722fe1-4523-5704-aa1c-8cb6ffc29cc2</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f2de5535-0d2e-5fe4-971b-d70bcab45f62_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_0e722fe1-4523-5704-aa1c-8cb6ffc29cc2_40000.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>ES|Catalonia|('seat',)|vehicle</t>
+          <t>ES|Catalonia|seat|vehicle</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>('ES', 'Catalonia', "('seat',)", 'vehicle')</t>
+          <t>('ES', 'Catalonia', 'seat', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Central Bohemia</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3947,22 +3947,22 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
+          <t>f1bee7e3-ba81-5e19-b58b-196acd14eee5</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f1bee7e3-ba81-5e19-b58b-196acd14eee5_120000.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
+          <t>CZ|Mladá Boleslav|skoda|vehicle</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
+          <t>('CZ', 'Mladá Boleslav', 'skoda', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Central Bohemia</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>69a8d694-a8ef-5977-9cb4-95e721a1c2b5</t>
+          <t>f1bee7e3-ba81-5e19-b58b-196acd14eee5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_69a8d694-a8ef-5977-9cb4-95e721a1c2b5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_f1bee7e3-ba81-5e19-b58b-196acd14eee5_nan</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|('skoda',)|vehicle</t>
+          <t>CZ|Mladá Boleslav|skoda|vehicle</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', "('skoda',)", 'vehicle')</t>
+          <t>('CZ', 'Mladá Boleslav', 'skoda', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Poissy</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4149,22 +4149,22 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>f0462b5a-ae72-5815-9d01-c0d999befd85</t>
+          <t>c47a324e-6321-503c-91b7-0768bf7aacd1</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f0462b5a-ae72-5815-9d01-c0d999befd85_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_c47a324e-6321-503c-91b7-0768bf7aacd1_40000.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>FR|Poissy|('srellantis',)|vehicle</t>
+          <t>FR|Poissy|srellantis|vehicle</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>('FR', 'Poissy', "('srellantis',)", 'vehicle')</t>
+          <t>('FR', 'Poissy', 'srellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4249,22 +4249,22 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
+          <t>7fa624ad-b486-5ad7-9e07-336e59b4497c</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7fa624ad-b486-5ad7-9e07-336e59b4497c_0.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>DE|Eisenach|('stellantis',)|vehicle</t>
+          <t>DE|Eisenach|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
+          <t>('DE', 'Eisenach', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4347,22 +4347,22 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>b4cab349-dacc-5f73-8e7b-483f322893e7</t>
+          <t>7fa624ad-b486-5ad7-9e07-336e59b4497c</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b4cab349-dacc-5f73-8e7b-483f322893e7_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_7fa624ad-b486-5ad7-9e07-336e59b4497c_nan</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>DE|Eisenach|('stellantis',)|vehicle</t>
+          <t>DE|Eisenach|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', "('stellantis',)", 'vehicle')</t>
+          <t>('DE', 'Eisenach', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4447,22 +4447,22 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
+          <t>185bfe94-4ed0-581e-add0-892e04a5c549</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_185bfe94-4ed0-581e-add0-892e04a5c549_80000.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
+          <t>SK|Trnava Region|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
+          <t>('SK', 'Trnava Region', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4545,22 +4545,22 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5</t>
+          <t>185bfe94-4ed0-581e-add0-892e04a5c549</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_3d932cba-5ffc-5a17-b4c0-f20c2d5ba0b5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_185bfe94-4ed0-581e-add0-892e04a5c549_nan</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|('stellantis',)|vehicle</t>
+          <t>SK|Trnava Region|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', "('stellantis',)", 'vehicle')</t>
+          <t>('SK', 'Trnava Region', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4645,22 +4645,22 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
+          <t>bfedd33e-0d82-5cf7-b457-ceb91fd44874</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_bfedd33e-0d82-5cf7-b457-ceb91fd44874_0.0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>ES|Galicia|('stellantis',)|vehicle</t>
+          <t>ES|Galicia|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
+          <t>('ES', 'Galicia', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4743,22 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>408c902f-cfa7-504a-9977-6439e267cf6f</t>
+          <t>bfedd33e-0d82-5cf7-b457-ceb91fd44874</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_408c902f-cfa7-504a-9977-6439e267cf6f_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_bfedd33e-0d82-5cf7-b457-ceb91fd44874_nan</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>ES|Galicia|('stellantis',)|vehicle</t>
+          <t>ES|Galicia|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', "('stellantis',)", 'vehicle')</t>
+          <t>('ES', 'Galicia', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Mulhouse</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>f04e6321-7663-5242-a582-e78bf30492fb</t>
+          <t>d396015a-27ec-52cc-a884-38634b3440fc</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f04e6321-7663-5242-a582-e78bf30492fb_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_d396015a-27ec-52cc-a884-38634b3440fc_60000.0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>FR|Mulhouse|('stellantis',)|vehicle</t>
+          <t>FR|Mulhouse|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>('FR', 'Mulhouse', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Mulhouse', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4951,22 +4951,22 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>0f1addfd-3731-5deb-905c-c1ca76aa8f8b</t>
+          <t>c6839a08-3a55-56cf-8d99-bae8dc08e9fc</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0f1addfd-3731-5deb-905c-c1ca76aa8f8b_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_c6839a08-3a55-56cf-8d99-bae8dc08e9fc_20000.0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>FR|Rennes|('stellantis',)|vehicle</t>
+          <t>FR|Rennes|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>('FR', 'Rennes', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Rennes', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bourgogne-Franche-Comté</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5055,22 +5055,22 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>69c19e84-42f0-5366-8453-cb02017d6f48</t>
+          <t>e140583d-c932-5b1a-87c6-1c48045a37be</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_69c19e84-42f0-5366-8453-cb02017d6f48_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_e140583d-c932-5b1a-87c6-1c48045a37be_40000.0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>FR|Sochaux|('stellantis',)|vehicle</t>
+          <t>FR|Sochaux|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>('FR', 'Sochaux', "('stellantis',)", 'vehicle')</t>
+          <t>('FR', 'Sochaux', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Hordain</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5159,22 +5159,22 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>6cf38a0c-36de-551b-9bcc-3cca04da0224</t>
+          <t>107a9a76-894e-5b6c-b9ce-b0e0125c4ee5</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6cf38a0c-36de-551b-9bcc-3cca04da0224_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_107a9a76-894e-5b6c-b9ce-b0e0125c4ee5_40000.0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>FR|Hordain|('stellantis (fiat chrysler)',)|vehicle</t>
+          <t>FR|Hordain|stellantis (fiat chrysler)|vehicle</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>('FR', 'Hordain', "('stellantis (fiat chrysler)',)", 'vehicle')</t>
+          <t>('FR', 'Hordain', 'stellantis (fiat chrysler)', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5259,22 +5259,22 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>e2b88591-16ed-593d-81d0-f4437853d855</t>
+          <t>29be1890-3777-517a-a337-0b7c8b408704</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_e2b88591-16ed-593d-81d0-f4437853d855_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_29be1890-3777-517a-a337-0b7c8b408704_20000.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>GB|Knowsley|('tata jlr',)|vehicle</t>
+          <t>GB|Knowsley|tata jlr|vehicle</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>('GB', 'Knowsley', "('tata jlr',)", 'vehicle')</t>
+          <t>('GB', 'Knowsley', 'tata jlr', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -5359,22 +5359,22 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>ab942289-b19a-5128-8112-1c5a42e60372</t>
+          <t>ab91c3dc-157c-56d7-8821-30a2e2611831</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ab942289-b19a-5128-8112-1c5a42e60372_320000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ab91c3dc-157c-56d7-8821-30a2e2611831_320000.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>DE|Berlin|('tesla',)|vehicle</t>
+          <t>DE|Berlin|tesla|vehicle</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>('DE', 'Berlin', "('tesla',)", 'vehicle')</t>
+          <t>('DE', 'Berlin', 'tesla', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Tilburg Municipality</t>
+          <t>North Brabant</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>868eec56-32a9-5703-bb1c-5381dda72cb9</t>
+          <t>9d2f4ecc-4678-516a-92a8-d0d995fe26c0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_868eec56-32a9-5703-bb1c-5381dda72cb9_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_9d2f4ecc-4678-516a-92a8-d0d995fe26c0_nan</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>NL|Tilburg Municipality|('tesla',)|vehicle</t>
+          <t>NL|Tilburg Municipality|tesla|vehicle</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>('NL', 'Tilburg Municipality', "('tesla',)", 'vehicle')</t>
+          <t>('NL', 'Tilburg Municipality', 'tesla', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>24f54170-5f2a-500a-8994-da2daf36ed6a</t>
+          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_24f54170-5f2a-500a-8994-da2daf36ed6a_140000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_140000.0</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|('volkswagen',)|vehicle</t>
+          <t>SK|Bratislava Region|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', "('volkswagen',)", 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Zwickau</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -5645,22 +5645,22 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>5407b64f-8759-5926-9898-d6b7600bdfe1</t>
+          <t>f4da068d-a297-54a5-a4ae-89eb4c1bc2d4</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5407b64f-8759-5926-9898-d6b7600bdfe1_500000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f4da068d-a297-54a5-a4ae-89eb4c1bc2d4_500000.0</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>DE|Zwickau|('volkswagen',)|vehicle</t>
+          <t>DE|Zwickau|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>('DE', 'Zwickau', "('volkswagen',)", 'vehicle')</t>
+          <t>('DE', 'Zwickau', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>Västra Götaland</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5745,22 +5745,22 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>67f70d66-387d-5b85-b56f-0c54abdc664f</t>
+          <t>018941f9-89ca-5292-bb96-95fcd1445d4f</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_67f70d66-387d-5b85-b56f-0c54abdc664f_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_018941f9-89ca-5292-bb96-95fcd1445d4f_120000.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SE|Gothenburg Municipality|('volvo',)|vehicle</t>
+          <t>SE|Gothenburg Municipality|volvo|vehicle</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>('SE', 'Gothenburg Municipality', "('volvo',)", 'vehicle')</t>
+          <t>('SE', 'Gothenburg Municipality', 'volvo', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5823,22 +5823,22 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1e021201-2d98-52e5-9905-7ccb21bf9a34</t>
+          <t>ae2c9a7d-e3ce-55a2-914c-aeb42bb12fbd</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1e021201-2d98-52e5-9905-7ccb21bf9a34_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_ae2c9a7d-e3ce-55a2-914c-aeb42bb12fbd_nan</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>FR|None|('volvo group',)|vehicle</t>
+          <t>FR|None|volvo group|vehicle</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>('FR', 'None', "('volvo group',)", 'vehicle')</t>
+          <t>('FR', 'None', 'volvo group', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5925,22 +5925,22 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>0fafaf96-5bec-51cc-a285-d4d9f2954cf3</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_0fafaf96-5bec-51cc-a285-d4d9f2954cf3_nan</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>BE|Arrondissement of Ghent|volvo group|vehicle</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', 'volvo group', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6027,22 +6027,22 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>bcdccb94-69aa-5c33-a476-6cd3838c0c57</t>
+          <t>0fafaf96-5bec-51cc-a285-d4d9f2954cf3</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bcdccb94-69aa-5c33-a476-6cd3838c0c57_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_0fafaf96-5bec-51cc-a285-d4d9f2954cf3_nan</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|('volvo group',)|vehicle</t>
+          <t>BE|Arrondissement of Ghent|volvo group|vehicle</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', "('volvo group',)", 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', 'volvo group', 'vehicle')</t>
         </is>
       </c>
     </row>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,37 +547,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bicester</t>
+          <t>győr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>40000</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44249</v>
+        <v>45657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -591,34 +593,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Cherwell District</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Bicester</t>
-        </is>
-      </c>
+          <t>Győr-Moson-Sopron</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>51.89998</v>
+        <v>47.68333</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.15357</v>
+        <v>17.63512</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -627,22 +617,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>b4377ec9-627e-56d9-8110-ee5e39a6f15b</t>
+          <t>33f0261c-2068-58e3-b6de-7de3feedf15d</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b4377ec9-627e-56d9-8110-ee5e39a6f15b_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_33f0261c-2068-58e3-b6de-7de3feedf15d_40000.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|arrival|vehicle</t>
+          <t>HU|Győr-Moson-Sopron|audi|vehicle</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', 'arrival', 'vehicle')</t>
+          <t>('HU', 'Győr-Moson-Sopron', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -654,34 +644,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>győr</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>győr</t>
+          <t>brussels</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45657</v>
+        <v>43252</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -695,22 +685,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Arrondissement Brussel-Hoofdstad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Brussels Capital</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Bruxelles-Capitale</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>47.68333</v>
+        <v>50.85045</v>
       </c>
       <c r="Q3" t="n">
-        <v>17.63512</v>
+        <v>4.34878</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -719,22 +717,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>33f0261c-2068-58e3-b6de-7de3feedf15d</t>
+          <t>72f60389-27c4-5075-b572-b6994992f5f9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_33f0261c-2068-58e3-b6de-7de3feedf15d_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_72f60389-27c4-5075-b572-b6994992f5f9_80000.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HU|Győr-Moson-Sopron|audi|vehicle</t>
+          <t>BE|Arrondissement Brussel-Hoofdstad|audi|vehicle</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>('HU', 'Győr-Moson-Sopron', 'audi', 'vehicle')</t>
+          <t>('BE', 'Arrondissement Brussel-Hoofdstad', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -746,34 +744,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brussels</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>43252</v>
+        <v>45292</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -787,30 +785,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bruxelles-Capitale</t>
+          <t>Upper Bavaria</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Arrondissement Brussel-Hoofdstad</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>Kreisfreie Stadt Ingolstadt</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>50.85045</v>
+        <v>48.76508</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.34878</v>
+        <v>11.42372</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -819,22 +821,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>72f60389-27c4-5075-b572-b6994992f5f9</t>
+          <t>318375f1-8e1f-5e1c-adc8-26827396c806</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_72f60389-27c4-5075-b572-b6994992f5f9_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_318375f1-8e1f-5e1c-adc8-26827396c806_20000.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>BE|Arrondissement Brussel-Hoofdstad|audi|vehicle</t>
+          <t>DE|Ingolstadt|audi|vehicle</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement Brussel-Hoofdstad', 'audi', 'vehicle')</t>
+          <t>('DE', 'Ingolstadt', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -846,12 +848,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>neckarsulm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -860,7 +862,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -869,11 +871,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45292</v>
+        <v>43983</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -887,34 +889,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Neckarsulm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Regierungsbezirk Stuttgart</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Ingolstadt</t>
+          <t>Landkreis Heilbronn</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Neckarsulm</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.76508</v>
+        <v>49.18912</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.42372</v>
+        <v>9.22527</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -923,39 +925,39 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>318375f1-8e1f-5e1c-adc8-26827396c806</t>
+          <t>1751b9ed-efe4-586f-9daa-1865eff86071</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_318375f1-8e1f-5e1c-adc8-26827396c806_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_1751b9ed-efe4-586f-9daa-1865eff86071_40000.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>DE|Ingolstadt|audi|vehicle</t>
+          <t>DE|Neckarsulm|audi|vehicle</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>('DE', 'Ingolstadt', 'audi', 'vehicle')</t>
+          <t>('DE', 'Neckarsulm', 'audi', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>neckarsulm</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -964,7 +966,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -973,11 +975,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>43983</v>
+        <v>45744</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -991,34 +993,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Regierungsbezirk Stuttgart</t>
+          <t>Upper Palatinate</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Landkreis Heilbronn</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Neckarsulm</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>49.18912</v>
+        <v>49.01513</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.22527</v>
+        <v>12.10161</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1027,22 +1029,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1751b9ed-efe4-586f-9daa-1865eff86071</t>
+          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1751b9ed-efe4-586f-9daa-1865eff86071_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_80000.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>DE|Neckarsulm|audi|vehicle</t>
+          <t>DE|Regensburg|bmw|vehicle</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>('DE', 'Neckarsulm', 'audi', 'vehicle')</t>
+          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1158,21 +1160,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>goodwood</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1185,7 +1187,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>41535</v>
+        <v>45291</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1197,33 +1199,13 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Saxony</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Kreisfreie Stadt Leipzig</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Leipzig</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>51.33962</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12.37129</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -1231,22 +1213,22 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
+          <t>909df65e-53ad-5d11-983c-19d2a628d5f9</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_909df65e-53ad-5d11-983c-19d2a628d5f9_0.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>DE|Leipzig|bmw|vehicle</t>
+          <t>GB|None|bmw|vehicle</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
+          <t>('GB', 'None', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1240,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>leipzig</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1285,7 +1267,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45355</v>
+        <v>44876</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1299,30 +1281,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Saxony</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Upper Palatinate</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Kreisfreie Stadt Leipzig</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Leipzig</t>
+          <t>Regensburg</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>51.33962</v>
+        <v>49.01513</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.37129</v>
+        <v>12.10161</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1331,22 +1317,22 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
+          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_160000.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DE|Leipzig|bmw|vehicle</t>
+          <t>DE|Regensburg|bmw|vehicle</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
+          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1448,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>dingolfing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1475,7 +1461,9 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>operational</t>
@@ -1483,11 +1471,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44491</v>
+        <v>42370</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1501,7 +1489,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Dingolfing</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1511,24 +1499,24 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Upper Bavaria</t>
+          <t>Lower Bavaria</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Munich, Urban District</t>
+          <t>Landkreis Dingolfing-Landau</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Dingolfing</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>48.13743</v>
+        <v>48.64244</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.57549</v>
+        <v>12.49283</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1537,22 +1525,22 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>afda602b-9bd5-55c2-9a85-fe15887ea212</t>
+          <t>d9373345-9500-5e3a-80b8-7311eaa846b7</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_afda602b-9bd5-55c2-9a85-fe15887ea212_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_d9373345-9500-5e3a-80b8-7311eaa846b7_40000.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>DE|Munich|bmw|vehicle</t>
+          <t>DE|Dingolfing|bmw|vehicle</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>('DE', 'Munich', 'bmw', 'vehicle')</t>
+          <t>('DE', 'Dingolfing', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1552,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1578,7 +1566,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1587,11 +1575,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44876</v>
+        <v>42369</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1605,34 +1593,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Bavaria</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Upper Palatinate</t>
-        </is>
-      </c>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>49.01513</v>
+        <v>51.33962</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.10161</v>
+        <v>12.37129</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1641,22 +1625,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
+          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_160000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_80000.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>DE|Regensburg|bmw|vehicle</t>
+          <t>DE|Leipzig|bmw|vehicle</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
+          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1652,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>leipzig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1682,7 +1666,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>240000</v>
+        <v>40000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1691,11 +1675,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45744</v>
+        <v>45657</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1709,34 +1693,30 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Bavaria</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Upper Palatinate</t>
-        </is>
-      </c>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Kreisfreie Stadt Leipzig</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Regensburg</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49.01513</v>
+        <v>51.33962</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.10161</v>
+        <v>12.37129</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1745,22 +1725,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ce4a102f-752e-5516-a5ce-1a9083f3b492</t>
+          <t>763c0003-024a-5daa-b621-949c3a9cc7d0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ce4a102f-752e-5516-a5ce-1a9083f3b492_240000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_763c0003-024a-5daa-b621-949c3a9cc7d0_40000.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>DE|Regensburg|bmw|vehicle</t>
+          <t>DE|Leipzig|bmw|vehicle</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>('DE', 'Regensburg', 'bmw', 'vehicle')</t>
+          <t>('DE', 'Leipzig', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1772,21 +1752,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cowley</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1799,7 +1779,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45657</v>
+        <v>44742</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1813,30 +1793,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Upper Bavaria</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Oxford</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>Munich, Urban District</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>51.73213</v>
+        <v>48.13743</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.20631</v>
+        <v>11.57549</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1845,22 +1829,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>474ec8c2-c923-55e9-9407-71ce51007407</t>
+          <t>afda602b-9bd5-55c2-9a85-fe15887ea212</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_474ec8c2-c923-55e9-9407-71ce51007407_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_afda602b-9bd5-55c2-9a85-fe15887ea212_160000.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>GB|Oxfordshire|bmw|vehicle</t>
+          <t>DE|Munich|bmw|vehicle</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>('GB', 'Oxfordshire', 'bmw', 'vehicle')</t>
+          <t>('DE', 'Munich', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1856,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>goodwood</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>goodwood</t>
+          <t>cowley</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1886,7 +1870,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1895,11 +1879,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45291</v>
+        <v>43830</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1911,13 +1895,33 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>51.73213</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.20631</v>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -1925,50 +1929,52 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>909df65e-53ad-5d11-983c-19d2a628d5f9</t>
+          <t>474ec8c2-c923-55e9-9407-71ce51007407</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_909df65e-53ad-5d11-983c-19d2a628d5f9_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_474ec8c2-c923-55e9-9407-71ce51007407_80000.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>GB|None|bmw|vehicle</t>
+          <t>GB|Oxfordshire|bmw|vehicle</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>('GB', 'None', 'bmw', 'vehicle')</t>
+          <t>('GB', 'Oxfordshire', 'bmw', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>allone</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>80000</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1977,7 +1983,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>43440</v>
+        <v>44196</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1989,13 +1995,33 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>39.47391</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.37966</v>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2003,44 +2029,44 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>ff42e3de-ca7c-5924-a756-d05062bfaac4</t>
+          <t>26f59fae-a89f-599f-94d0-a4e53b275c21</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ff42e3de-ca7c-5924-a756-d05062bfaac4_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_26f59fae-a89f-599f-94d0-a4e53b275c21_80000.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>FR|None|byd|vehicle</t>
+          <t>ES|Valencia|ford|vehicle</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>('FR', 'None', 'byd', 'vehicle')</t>
+          <t>('ES', 'Valencia', 'ford', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>ford otosan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>dolj</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>komárom</t>
+          <t>dolj</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2053,11 +2079,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>42855</v>
+        <v>45657</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2069,25 +2095,13 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Komárom-Esztergom</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Komárom-Esztergom</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>47.74318</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>18.11913</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2095,48 +2109,48 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>41140c52-225e-5738-beaa-13145ea3cf59</t>
+          <t>aeb6b6a5-e09a-5aeb-8372-eab9c4d2c261</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_41140c52-225e-5738-beaa-13145ea3cf59_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_aeb6b6a5-e09a-5aeb-8372-eab9c4d2c261_0.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>HU|Komárom-Esztergom|byd|vehicle</t>
+          <t>RO|None|ford otosan|vehicle</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>('HU', 'Komárom-Esztergom', 'byd', 'vehicle')</t>
+          <t>('RO', 'None', 'ford otosan', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>hyundai</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cologne</t>
+          <t>nošovice</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>360000</v>
+        <v>120000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2149,7 +2163,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45447</v>
+        <v>43891</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2163,34 +2177,30 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Cologne</t>
+          <t>Nošovice</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Moravskoslezský</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Cologne District</t>
+          <t>Okres Frýdek-Místek</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cologne, Urban District</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Cologne</t>
-        </is>
-      </c>
+          <t>Nošovice</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>50.93333</v>
+        <v>49.66073</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.95</v>
+        <v>18.42633</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2199,48 +2209,48 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>b42f04b4-6b19-5f3e-9dbb-b7e98880b5ad</t>
+          <t>60d7afdf-9005-53df-ab21-93ee3d549c47</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_b42f04b4-6b19-5f3e-9dbb-b7e98880b5ad_360000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_60d7afdf-9005-53df-ab21-93ee3d549c47_120000.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>DE|Cologne|ford|vehicle</t>
+          <t>CZ|Nošovice|hyundai|vehicle</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>('DE', 'Cologne', 'ford', 'vehicle')</t>
+          <t>('CZ', 'Nošovice', 'hyundai', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hyundai</t>
+          <t>kia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nošovice</t>
+          <t>žilina</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2253,7 +2263,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>43891</v>
+        <v>44196</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2267,30 +2277,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Nošovice</t>
+          <t>Žilina Region</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Moravskoslezský</t>
+          <t>Žilina Region</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Okres Frýdek-Místek</t>
+          <t>Žilina District</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Nošovice</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>49.66073</v>
+        <v>49.22315</v>
       </c>
       <c r="Q19" t="n">
-        <v>18.42633</v>
+        <v>18.73941</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2299,49 +2309,47 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>60d7afdf-9005-53df-ab21-93ee3d549c47</t>
+          <t>28bf3caf-06c8-5191-98cb-97c7ea26be54</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_60d7afdf-9005-53df-ab21-93ee3d549c47_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_28bf3caf-06c8-5191-98cb-97c7ea26be54_60000.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>CZ|Nošovice|hyundai|vehicle</t>
+          <t>SK|Žilina Region|kia|vehicle</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>('CZ', 'Nošovice', 'hyundai', 'vehicle')</t>
+          <t>('SK', 'Žilina Region', 'kia', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kia</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>žilina</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>60000</v>
-      </c>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>operational</t>
@@ -2349,11 +2357,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45657</v>
+        <v>45261</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2365,33 +2373,13 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Žilina Region</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Žilina Region</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Žilina District</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Žilina</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>49.22315</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>18.73941</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2399,22 +2387,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>28bf3caf-06c8-5191-98cb-97c7ea26be54</t>
+          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_28bf3caf-06c8-5191-98cb-97c7ea26be54_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_nan</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SK|Žilina Region|kia|vehicle</t>
+          <t>DE|None|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>('SK', 'Žilina Region', 'kia', 'vehicle')</t>
+          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2414,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bremen</t>
+          <t>dussendorf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2440,7 +2428,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2453,7 +2441,7 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>42005</v>
+        <v>43831</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2465,33 +2453,13 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Bremen</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>City state Bremen</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Kreisfreie Stadt Bremen</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Bremen</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>53.07582</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8.807169999999999</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2499,22 +2467,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>a872b950-3bbe-50cf-8d40-35d08fc41ecc</t>
+          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_a872b950-3bbe-50cf-8d40-35d08fc41ecc_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_0.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>DE|Bremen|mercedes benz|vehicle</t>
+          <t>DE|None|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>('DE', 'Bremen', 'mercedes benz', 'vehicle')</t>
+          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>rastatt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2540,7 +2508,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2553,7 +2521,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43831</v>
+        <v>43102</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2565,13 +2533,37 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Rastatt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baden-Wurttemberg</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Karlsruhe Region</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Landkreis Rastatt</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Rastatt</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>48.85851</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8.20965</v>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2579,22 +2571,22 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
+          <t>a138278e-fa43-5700-9479-61f888ac0dde</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a138278e-fa43-5700-9479-61f888ac0dde_120000.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>DE|None|mercedes benz|vehicle</t>
+          <t>DE|Rastatt|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
+          <t>('DE', 'Rastatt', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2598,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dussendorf</t>
+          <t>sindelfingen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2619,7 +2611,9 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>80000</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>operational</t>
@@ -2627,11 +2621,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45261</v>
+        <v>42370</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2643,13 +2637,37 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Sindelfingen</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Baden-Wurttemberg</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Stuttgart</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Landkreis Böblingen</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sindelfingen</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.01667</v>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2657,22 +2675,22 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>47e58326-470c-50d7-9d9c-35d8ae6d660f</t>
+          <t>81687d9c-3bf4-5901-9814-be851b7e03d1</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_47e58326-470c-50d7-9d9c-35d8ae6d660f_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_81687d9c-3bf4-5901-9814-be851b7e03d1_80000.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>DE|None|mercedes benz|vehicle</t>
+          <t>DE|Sindelfingen|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>('DE', 'None', 'mercedes benz', 'vehicle')</t>
+          <t>('DE', 'Sindelfingen', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2702,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rastatt</t>
+          <t>bremen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2698,7 +2716,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2711,7 +2729,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>43102</v>
+        <v>42005</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2725,34 +2743,30 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rastatt</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Karlsruhe Region</t>
-        </is>
-      </c>
+          <t>City state Bremen</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Landkreis Rastatt</t>
+          <t>Kreisfreie Stadt Bremen</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Rastatt</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>48.85851</v>
+        <v>53.07582</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.20965</v>
+        <v>8.807169999999999</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2761,22 +2775,22 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>a138278e-fa43-5700-9479-61f888ac0dde</t>
+          <t>a872b950-3bbe-50cf-8d40-35d08fc41ecc</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_a138278e-fa43-5700-9479-61f888ac0dde_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_a872b950-3bbe-50cf-8d40-35d08fc41ecc_40000.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>DE|Rastatt|mercedes benz|vehicle</t>
+          <t>DE|Bremen|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>('DE', 'Rastatt', 'mercedes benz', 'vehicle')</t>
+          <t>('DE', 'Bremen', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2788,17 +2802,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sindelfingen</t>
+          <t>kecskemet</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2815,7 +2829,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>42370</v>
+        <v>44530</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2829,34 +2843,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sindelfingen</t>
+          <t>Bács-Kiskun</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Regierungsbezirk Stuttgart</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Landkreis Böblingen</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Sindelfingen</t>
-        </is>
-      </c>
+          <t>Bács-Kiskun</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>48.7</v>
+        <v>46.90618</v>
       </c>
       <c r="Q25" t="n">
-        <v>9.01667</v>
+        <v>19.69128</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2865,22 +2867,22 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>81687d9c-3bf4-5901-9814-be851b7e03d1</t>
+          <t>0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_81687d9c-3bf4-5901-9814-be851b7e03d1_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2_80000.0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>DE|Sindelfingen|mercedes benz|vehicle</t>
+          <t>HU|Bács-Kiskun|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>('DE', 'Sindelfingen', 'mercedes benz', 'vehicle')</t>
+          <t>('HU', 'Bács-Kiskun', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2894,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>vitoria-gasteiz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>vitoria</t>
+          <t>vitoriagasteiz</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2931,13 +2933,33 @@
           <t>electric</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Basque Country</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Araba / Álava</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>42.84998</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.67268</v>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
@@ -2945,48 +2967,48 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>6862c608-86bf-5b3c-a51f-b20faa029caa</t>
+          <t>5024cb92-04bb-5923-8456-1aaca8bbc481</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_6862c608-86bf-5b3c-a51f-b20faa029caa_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5024cb92-04bb-5923-8456-1aaca8bbc481_20000.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>ES|None|mercedes benz|vehicle</t>
+          <t>ES|Vitoria-Gasteiz|mercedes benz|vehicle</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>('ES', 'None', 'mercedes benz', 'vehicle')</t>
+          <t>('ES', 'Vitoria-Gasteiz', 'mercedes benz', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kecskemet</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2995,11 +3017,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44530</v>
+        <v>41275</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3013,22 +3035,26 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Bács-Kiskun</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Bács-Kiskun</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>46.90618</v>
+        <v>54.90465</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.69128</v>
+        <v>-1.38222</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -3037,48 +3063,48 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2</t>
+          <t>5e64d344-4569-5f9e-bf88-fa88fa5f55de</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0c49c7cf-99fc-5178-bcf3-7bfdd76a4ab2_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5e64d344-4569-5f9e-bf88-fa88fa5f55de_60000.0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>HU|Bács-Kiskun|mercedes benz|vehicle</t>
+          <t>GB|Sunderland|nissan|vehicle</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>('HU', 'Bács-Kiskun', 'mercedes benz', 'vehicle')</t>
+          <t>('GB', 'Sunderland', 'nissan', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3091,7 +3117,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>41275</v>
+        <v>45657</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3105,26 +3131,34 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Sunderland</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Arrondissement of Avesnes-sur-Helpe</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Maubeuge</t>
+        </is>
+      </c>
       <c r="P28" t="n">
-        <v>54.90465</v>
+        <v>50.27875</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.38222</v>
+        <v>3.97267</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3133,22 +3167,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>5e64d344-4569-5f9e-bf88-fa88fa5f55de</t>
+          <t>ae2d47e1-87d3-57a5-a054-c96dec440280</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5e64d344-4569-5f9e-bf88-fa88fa5f55de_60000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_40000.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>GB|Sunderland|nissan|vehicle</t>
+          <t>FR|Maubeuge|renault|vehicle</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>('GB', 'Sunderland', 'nissan', 'vehicle')</t>
+          <t>('FR', 'Maubeuge', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3194,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>maubeuge</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>maubeuge</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3174,7 +3208,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3201,34 +3235,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Maubeuge</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Meurthe et Moselle</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Arrondissement of Avesnes-sur-Helpe</t>
+          <t>Arrondissement of Briey</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Maubeuge</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>50.27875</v>
+        <v>49.17372</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97267</v>
+        <v>5.96869</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3237,22 +3271,22 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>ae2d47e1-87d3-57a5-a054-c96dec440280</t>
+          <t>307c4123-5be8-5174-ad9d-1840e75df719</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_307c4123-5be8-5174-ad9d-1840e75df719_0.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>FR|Maubeuge|renault|vehicle</t>
+          <t>FR|Batilly|renault|vehicle</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>('FR', 'Maubeuge', 'renault', 'vehicle')</t>
+          <t>('FR', 'Batilly', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3298,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>sandouville</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3305,34 +3339,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Sandouville</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Meurthe et Moselle</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Arrondissement of Briey</t>
+          <t>Arrondissement of Le Havre</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Sandouville</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>49.17372</v>
+        <v>49.4978</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.96869</v>
+        <v>0.31748</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3341,22 +3375,22 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>307c4123-5be8-5174-ad9d-1840e75df719</t>
+          <t>424b7ed5-fc12-5e41-b341-a5b1dde327f5</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_307c4123-5be8-5174-ad9d-1840e75df719_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_424b7ed5-fc12-5e41-b341-a5b1dde327f5_0.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>FR|Batilly|renault|vehicle</t>
+          <t>FR|Sandouville|renault|vehicle</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>('FR', 'Batilly', 'renault', 'vehicle')</t>
+          <t>('FR', 'Sandouville', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3402,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>flins</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>flins</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3382,7 +3416,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,7 +3429,7 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3409,34 +3443,34 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Flins-sur-Seine</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>North</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Arrondissement of Mantes-la-Jolie</t>
+          <t>Arrondissement of Douai</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Flins-sur-Seine</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>48.96523</v>
+        <v>50.37069</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.87314</v>
+        <v>3.07922</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3445,22 +3479,22 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>5140a707-9f43-506f-868e-0bce2129328e</t>
+          <t>252dc9b3-ab0a-55e9-873c-064f96c53ea6</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_80000.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>FR|Flins-sur-Seine|renault|vehicle</t>
+          <t>FR|Douai|renault|vehicle</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>('FR', 'Flins-sur-Seine', 'renault', 'vehicle')</t>
+          <t>('FR', 'Douai', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3506,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>douai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3486,7 +3520,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3495,7 +3529,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -3513,34 +3547,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>North</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Arrondissement of Le Havre</t>
+          <t>Arrondissement of Douai</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Douai</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>49.4978</v>
+        <v>50.37069</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.31748</v>
+        <v>3.07922</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3549,22 +3583,22 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>424b7ed5-fc12-5e41-b341-a5b1dde327f5</t>
+          <t>252dc9b3-ab0a-55e9-873c-064f96c53ea6</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_424b7ed5-fc12-5e41-b341-a5b1dde327f5_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_120000.0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>FR|Sandouville|renault|vehicle</t>
+          <t>FR|Douai|renault|vehicle</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>('FR', 'Sandouville', 'renault', 'vehicle')</t>
+          <t>('FR', 'Douai', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3610,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3590,7 +3624,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3603,7 +3637,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3617,34 +3651,34 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Arrondissement of Douai</t>
+          <t>Arrondissement of Mantes-la-Jolie</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>50.37069</v>
+        <v>48.96523</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.07922</v>
+        <v>1.87314</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3653,47 +3687,49 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>252dc9b3-ab0a-55e9-873c-064f96c53ea6</t>
+          <t>5140a707-9f43-506f-868e-0bce2129328e</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_40000.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>FR|Douai|renault|vehicle</t>
+          <t>FR|Flins-sur-Seine|renault|vehicle</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>('FR', 'Douai', 'renault', 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rimac automobili</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>veliko trgovišće</t>
+          <t>novo mesto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>veliko_trgovišće</t>
+          <t>novo_mesto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>40000</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>operational</t>
@@ -3705,7 +3741,7 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45583</v>
+        <v>44196</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3719,26 +3755,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Krapina-Zagorje</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Krapina-Zagorje</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Municipality of Veliko Trgovišće</t>
-        </is>
-      </c>
+          <t>Novo Mesto</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>46</v>
+        <v>45.80397</v>
       </c>
       <c r="Q34" t="n">
-        <v>15.85</v>
+        <v>15.16886</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3747,22 +3779,22 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>df7be9cf-b360-575d-9cfa-de4b0f37a3a4</t>
+          <t>cae893de-e792-5121-b6a8-75f1cf517027</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_df7be9cf-b360-575d-9cfa-de4b0f37a3a4_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_cae893de-e792-5121-b6a8-75f1cf517027_40000.0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>HR|Krapina-Zagorje|rimac automobili|vehicle</t>
+          <t>SI|Novo Mesto|renault|vehicle</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>('HR', 'Krapina-Zagorje', 'rimac automobili', 'vehicle')</t>
+          <t>('SI', 'Novo Mesto', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3820,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3801,7 +3833,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>43831</v>
+        <v>44197</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3815,7 +3847,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Martorell</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3847,22 +3879,22 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0e722fe1-4523-5704-aa1c-8cb6ffc29cc2</t>
+          <t>fd4bfcba-5859-5681-a582-2f56b17afe5d</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_0e722fe1-4523-5704-aa1c-8cb6ffc29cc2_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_fd4bfcba-5859-5681-a582-2f56b17afe5d_80000.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>ES|Catalonia|seat|vehicle</t>
+          <t>ES|Martorell|seat|vehicle</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>('ES', 'Catalonia', 'seat', 'vehicle')</t>
+          <t>('ES', 'Martorell', 'seat', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3969,37 +4001,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>skoda</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mladá boleslav</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mladá_boleslav</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>40000</v>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45679</v>
+        <v>45291</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4013,30 +4047,34 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Poissy</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Central Bohemia</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav District</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>Arrondissement of Saint-Germain-en-Laye</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Poissy</t>
+        </is>
+      </c>
       <c r="P37" t="n">
-        <v>50.41135</v>
+        <v>48.92902</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.90318</v>
+        <v>2.04952</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4045,61 +4083,59 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>f1bee7e3-ba81-5e19-b58b-196acd14eee5</t>
+          <t>1a826860-cc3f-5c7d-9e41-ab9563a927fc</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f1bee7e3-ba81-5e19-b58b-196acd14eee5_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_1a826860-cc3f-5c7d-9e41-ab9563a927fc_40000.0</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|skoda|vehicle</t>
+          <t>FR|Poissy|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', 'skoda', 'vehicle')</t>
+          <t>('FR', 'Poissy', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>srellantis</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>40000</v>
-      </c>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45291</v>
+        <v>44502</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4113,34 +4149,30 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Poissy</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Arrondissement of Saint-Germain-en-Laye</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Poissy</t>
-        </is>
-      </c>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>48.92902</v>
+        <v>42.23282</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.04952</v>
+        <v>-8.72264</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4149,22 +4181,22 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>c47a324e-6321-503c-91b7-0768bf7aacd1</t>
+          <t>5ffe50f9-d148-5c9a-9d53-5afd17293ea1</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_c47a324e-6321-503c-91b7-0768bf7aacd1_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5ffe50f9-d148-5c9a-9d53-5afd17293ea1_nan</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>FR|Poissy|srellantis|vehicle</t>
+          <t>ES|Vigo|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>('FR', 'Poissy', 'srellantis', 'vehicle')</t>
+          <t>('ES', 'Vigo', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4176,21 +4208,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>trnava</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4203,7 +4235,7 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>43831</v>
+        <v>43559</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4217,30 +4249,30 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Thuringia</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Trnava District</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Wartburgkreis</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
+          <t>Trnava</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>50.9807</v>
+        <v>48.37741</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.31522</v>
+        <v>17.58723</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4249,22 +4281,22 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>7fa624ad-b486-5ad7-9e07-336e59b4497c</t>
+          <t>185bfe94-4ed0-581e-add0-892e04a5c549</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7fa624ad-b486-5ad7-9e07-336e59b4497c_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_185bfe94-4ed0-581e-add0-892e04a5c549_80000.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>DE|Eisenach|stellantis|vehicle</t>
+          <t>SK|Trnava Region|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', 'stellantis', 'vehicle')</t>
+          <t>('SK', 'Trnava Region', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4276,20 +4308,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>eisenach</t>
+          <t>vigo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4297,11 +4331,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45536</v>
+        <v>41061</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4315,30 +4349,30 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Eisenach</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Thuringia</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Pontevedra</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Wartburgkreis</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Eisenach</t>
-        </is>
-      </c>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>50.9807</v>
+        <v>42.23282</v>
       </c>
       <c r="Q40" t="n">
-        <v>10.31522</v>
+        <v>-8.72264</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -4347,22 +4381,22 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>7fa624ad-b486-5ad7-9e07-336e59b4497c</t>
+          <t>5ffe50f9-d148-5c9a-9d53-5afd17293ea1</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_7fa624ad-b486-5ad7-9e07-336e59b4497c_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_5ffe50f9-d148-5c9a-9d53-5afd17293ea1_0.0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>DE|Eisenach|stellantis|vehicle</t>
+          <t>ES|Vigo|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>('DE', 'Eisenach', 'stellantis', 'vehicle')</t>
+          <t>('ES', 'Vigo', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4374,25 +4408,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>eisenach</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4401,7 +4435,7 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43559</v>
+        <v>43831</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4415,30 +4449,30 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Eisenach</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Trnava District</t>
-        </is>
-      </c>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Trnava</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>Wartburgkreis</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Eisenach</t>
+        </is>
+      </c>
       <c r="P41" t="n">
-        <v>48.37741</v>
+        <v>50.9807</v>
       </c>
       <c r="Q41" t="n">
-        <v>17.58723</v>
+        <v>10.31522</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -4447,22 +4481,22 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>185bfe94-4ed0-581e-add0-892e04a5c549</t>
+          <t>7fa624ad-b486-5ad7-9e07-336e59b4497c</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_185bfe94-4ed0-581e-add0-892e04a5c549_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_7fa624ad-b486-5ad7-9e07-336e59b4497c_0.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|stellantis|vehicle</t>
+          <t>DE|Eisenach|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', 'stellantis', 'vehicle')</t>
+          <t>('DE', 'Eisenach', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4474,23 +4508,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>ellesmere port</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>trnava</t>
+          <t>ellesmere_port</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>20000</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4499,7 +4535,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45108</v>
+        <v>44742</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4513,30 +4549,30 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Cheshire</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Trnava District</t>
+          <t>Cheshire</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Trnava</t>
+          <t>Little Stanney</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>48.37741</v>
+        <v>53.27875</v>
       </c>
       <c r="Q42" t="n">
-        <v>17.58723</v>
+        <v>-2.90134</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -4545,22 +4581,22 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>185bfe94-4ed0-581e-add0-892e04a5c549</t>
+          <t>a6e48178-9999-5a41-b898-608ac2d2e0d8</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_185bfe94-4ed0-581e-add0-892e04a5c549_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_a6e48178-9999-5a41-b898-608ac2d2e0d8_20000.0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SK|Trnava Region|stellantis|vehicle</t>
+          <t>GB|Cheshire|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>('SK', 'Trnava Region', 'stellantis', 'vehicle')</t>
+          <t>('GB', 'Cheshire', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4572,21 +4608,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>sochaux</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>sochaux</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4595,11 +4631,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41061</v>
+        <v>45657</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4613,30 +4649,34 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Bourgogne-Franche-Comté</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Doubs</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Vigo</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>Arrondissement of Montbéliard</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
       <c r="P43" t="n">
-        <v>42.23282</v>
+        <v>47.50808</v>
       </c>
       <c r="Q43" t="n">
-        <v>-8.72264</v>
+        <v>6.82748</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4645,22 +4685,22 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>bfedd33e-0d82-5cf7-b457-ceb91fd44874</t>
+          <t>e140583d-c932-5b1a-87c6-1c48045a37be</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bfedd33e-0d82-5cf7-b457-ceb91fd44874_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_e140583d-c932-5b1a-87c6-1c48045a37be_40000.0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>ES|Galicia|stellantis|vehicle</t>
+          <t>FR|Sochaux|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', 'stellantis', 'vehicle')</t>
+          <t>('FR', 'Sochaux', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4672,32 +4712,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>hordain</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>hordain</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>40000</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44502</v>
+        <v>45657</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4711,30 +4753,34 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Hordain</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>North</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Vigo</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>Arrondissement of Valenciennes</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Hordain</t>
+        </is>
+      </c>
       <c r="P44" t="n">
-        <v>42.23282</v>
+        <v>50.26306</v>
       </c>
       <c r="Q44" t="n">
-        <v>-8.72264</v>
+        <v>3.31358</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4743,22 +4789,22 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>bfedd33e-0d82-5cf7-b457-ceb91fd44874</t>
+          <t>50b21bff-1027-5caa-8620-07422f580482</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_bfedd33e-0d82-5cf7-b457-ceb91fd44874_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_50b21bff-1027-5caa-8620-07422f580482_40000.0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>ES|Galicia|stellantis|vehicle</t>
+          <t>FR|Hordain|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>('ES', 'Galicia', 'stellantis', 'vehicle')</t>
+          <t>('FR', 'Hordain', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4973,26 +5019,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>tata jlr</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sochaux</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sochaux</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5001,11 +5047,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45657</v>
+        <v>43101</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5019,34 +5065,30 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Bourgogne-Franche-Comté</t>
+          <t>England</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Doubs</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Arrondissement of Montbéliard</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Sochaux</t>
-        </is>
-      </c>
+          <t>Halewood</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>47.50808</v>
+        <v>53.36434</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.82748</v>
+        <v>-2.82053</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -5055,61 +5097,61 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>e140583d-c932-5b1a-87c6-1c48045a37be</t>
+          <t>29be1890-3777-517a-a337-0b7c8b408704</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_e140583d-c932-5b1a-87c6-1c48045a37be_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_29be1890-3777-517a-a337-0b7c8b408704_20000.0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>FR|Sochaux|stellantis|vehicle</t>
+          <t>GB|Knowsley|tata jlr|vehicle</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>('FR', 'Sochaux', 'stellantis', 'vehicle')</t>
+          <t>('GB', 'Knowsley', 'tata jlr', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stellantis (fiat chrysler)</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hordain</t>
+          <t>grünheide</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hordain</t>
+          <t>grünheide</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>40000</v>
+        <v>320000</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5123,34 +5165,30 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Hordain</t>
+          <t>Grünheide (Mark)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Arrondissement of Valenciennes</t>
+          <t>Landkreis Oder-Spree</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Hordain</t>
+          <t>Grünheide (Mark)</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>50.26306</v>
+        <v>52.42343</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.31358</v>
+        <v>13.81324</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5159,48 +5197,48 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>107a9a76-894e-5b6c-b9ce-b0e0125c4ee5</t>
+          <t>aa7e8a02-3dc6-59cf-bae6-5488cdc58c62</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_107a9a76-894e-5b6c-b9ce-b0e0125c4ee5_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_aa7e8a02-3dc6-59cf-bae6-5488cdc58c62_320000.0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>FR|Hordain|stellantis (fiat chrysler)|vehicle</t>
+          <t>DE|Grünheide (Mark)|tesla|vehicle</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>('FR', 'Hordain', 'stellantis (fiat chrysler)', 'vehicle')</t>
+          <t>('DE', 'Grünheide (Mark)', 'tesla', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tata jlr</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>hanover</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>hanover</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5209,11 +5247,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43101</v>
+        <v>44926</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5227,30 +5265,30 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hanover</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Knowsley</t>
-        </is>
-      </c>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Halewood</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>Region Hannover</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
       <c r="P49" t="n">
-        <v>53.36434</v>
+        <v>52.37052</v>
       </c>
       <c r="Q49" t="n">
-        <v>-2.82053</v>
+        <v>9.733219999999999</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5259,48 +5297,48 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>29be1890-3777-517a-a337-0b7c8b408704</t>
+          <t>f50f1baf-752f-5614-a4b3-9dc9071ee0e9</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_29be1890-3777-517a-a337-0b7c8b408704_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f50f1baf-752f-5614-a4b3-9dc9071ee0e9_40000.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>GB|Knowsley|tata jlr|vehicle</t>
+          <t>DE|Hanover|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>('GB', 'Knowsley', 'tata jlr', 'vehicle')</t>
+          <t>('DE', 'Hanover', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>320000</v>
+        <v>20000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5313,7 +5351,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44642</v>
+        <v>43830</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5327,30 +5365,22 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Berlin, Stadt</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>52.52437</v>
+        <v>48.14816</v>
       </c>
       <c r="Q50" t="n">
-        <v>13.41053</v>
+        <v>17.10674</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5359,59 +5389,61 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>ab91c3dc-157c-56d7-8821-30a2e2611831</t>
+          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ab91c3dc-157c-56d7-8821-30a2e2611831_320000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_20000.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>DE|Berlin|tesla|vehicle</t>
+          <t>SK|Bratislava Region|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>('DE', 'Berlin', 'tesla', 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tilburg</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>140000</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>42157</v>
+        <v>45291</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5425,26 +5457,22 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tilburg Municipality</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>North Brabant</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Tilburg Municipality</t>
-        </is>
-      </c>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>51.55551</v>
+        <v>48.14816</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.0913</v>
+        <v>17.10674</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5453,48 +5481,48 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>9d2f4ecc-4678-516a-92a8-d0d995fe26c0</t>
+          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_9d2f4ecc-4678-516a-92a8-d0d995fe26c0_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_140000.0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>NL|Tilburg Municipality|tesla|vehicle</t>
+          <t>SK|Bratislava Region|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>('NL', 'Tilburg Municipality', 'tesla', 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>volvo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>140000</v>
+        <v>120000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5503,11 +5531,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41426</v>
+        <v>45657</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5521,22 +5549,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Gothenburg Municipality</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Gothenburg Municipality</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Torslanda</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>48.14816</v>
+        <v>57.72504</v>
       </c>
       <c r="Q52" t="n">
-        <v>17.10674</v>
+        <v>11.76903</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5545,48 +5581,48 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
+          <t>018941f9-89ca-5292-bb96-95fcd1445d4f</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_140000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_018941f9-89ca-5292-bb96-95fcd1445d4f_120000.0</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|volkswagen|vehicle</t>
+          <t>SE|Gothenburg Municipality|volvo|vehicle</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
+          <t>('SE', 'Gothenburg Municipality', 'volvo', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>volvo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>zwickau</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>500000</v>
+        <v>40000</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5595,11 +5631,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43773</v>
+        <v>44196</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5613,30 +5649,34 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Zwickau</t>
+          <t>Arrondissement of Ghent</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Saxony</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>Flanders</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>East Flanders Province</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Zwickau</t>
+          <t>Arrondissement of Ghent</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Zwickau</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>50.72724</v>
+        <v>51.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>12.48839</v>
+        <v>3.71667</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5645,22 +5685,22 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>f4da068d-a297-54a5-a4ae-89eb4c1bc2d4</t>
+          <t>8727a516-7052-5f8b-a9da-0c21cb46ec42</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f4da068d-a297-54a5-a4ae-89eb4c1bc2d4_500000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_8727a516-7052-5f8b-a9da-0c21cb46ec42_40000.0</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>DE|Zwickau|volkswagen|vehicle</t>
+          <t>BE|Arrondissement of Ghent|volvo|vehicle</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>('DE', 'Zwickau', 'volkswagen', 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', 'volvo', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5672,21 +5712,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>ghent</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5695,7 +5735,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -5713,30 +5753,34 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>Arrondissement of Ghent</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Västra Götaland</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>East Flanders Province</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Torslanda</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
       <c r="P54" t="n">
-        <v>57.72504</v>
+        <v>51.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.76903</v>
+        <v>3.71667</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -5745,304 +5789,22 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>018941f9-89ca-5292-bb96-95fcd1445d4f</t>
+          <t>8727a516-7052-5f8b-a9da-0c21cb46ec42</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_018941f9-89ca-5292-bb96-95fcd1445d4f_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_8727a516-7052-5f8b-a9da-0c21cb46ec42_200000.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SE|Gothenburg Municipality|volvo|vehicle</t>
+          <t>BE|Arrondissement of Ghent|volvo|vehicle</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>('SE', 'Gothenburg Municipality', 'volvo', 'vehicle')</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>volvo group</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>blainville</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>blainville</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>greenfield</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>43646</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ae2c9a7d-e3ce-55a2-914c-aeb42bb12fbd</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa_ae2c9a7d-e3ce-55a2-914c-aeb42bb12fbd_nan</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>FR|None|volvo group|vehicle</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>('FR', 'None', 'volvo group', 'vehicle')</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>volvo group</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ghent</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ghent</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>greenfield</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>45183</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Flanders</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>East Flanders Province</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.71667</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>0fafaf96-5bec-51cc-a285-d4d9f2954cf3</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa_0fafaf96-5bec-51cc-a285-d4d9f2954cf3_nan</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>BE|Arrondissement of Ghent|volvo group|vehicle</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>('BE', 'Arrondissement of Ghent', 'volvo group', 'vehicle')</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>volvo group</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>ghent</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ghent</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>expansion</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>45777</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>vehicle</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Flanders</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>East Flanders Province</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.71667</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>0fafaf96-5bec-51cc-a285-d4d9f2954cf3</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>68d684fc1c2e9d8ed1487afa_0fafaf96-5bec-51cc-a285-d4d9f2954cf3_nan</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>BE|Arrondissement of Ghent|volvo group|vehicle</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>('BE', 'Arrondissement of Ghent', 'volvo group', 'vehicle')</t>
+          <t>('BE', 'Arrondissement of Ghent', 'volvo', 'vehicle')</t>
         </is>
       </c>
     </row>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3113,11 +3113,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45657</v>
+        <v>40908</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_20000.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>batilly</t>
+          <t>maubeuge</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3217,11 +3217,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3235,34 +3235,34 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Meurthe et Moselle</t>
+          <t>North</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Arrondissement of Briey</t>
+          <t>Arrondissement of Avesnes-sur-Helpe</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Batilly</t>
+          <t>Maubeuge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>49.17372</v>
+        <v>50.27875</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.96869</v>
+        <v>3.97267</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>307c4123-5be8-5174-ad9d-1840e75df719</t>
+          <t>ae2d47e1-87d3-57a5-a054-c96dec440280</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_307c4123-5be8-5174-ad9d-1840e75df719_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_ae2d47e1-87d3-57a5-a054-c96dec440280_40000.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>FR|Batilly|renault|vehicle</t>
+          <t>FR|Maubeuge|renault|vehicle</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>('FR', 'Batilly', 'renault', 'vehicle')</t>
+          <t>('FR', 'Maubeuge', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sandouville</t>
+          <t>batilly</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45657</v>
+        <v>43830</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3339,34 +3339,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Meurthe et Moselle</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Arrondissement of Le Havre</t>
+          <t>Arrondissement of Briey</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sandouville</t>
+          <t>Batilly</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>49.4978</v>
+        <v>49.17372</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.31748</v>
+        <v>5.96869</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3375,22 +3375,22 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>424b7ed5-fc12-5e41-b341-a5b1dde327f5</t>
+          <t>307c4123-5be8-5174-ad9d-1840e75df719</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_424b7ed5-fc12-5e41-b341-a5b1dde327f5_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_307c4123-5be8-5174-ad9d-1840e75df719_0.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>FR|Sandouville|renault|vehicle</t>
+          <t>FR|Batilly|renault|vehicle</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>('FR', 'Sandouville', 'renault', 'vehicle')</t>
+          <t>('FR', 'Batilly', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3425,11 +3425,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_120000.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>douai</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3529,11 +3529,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45657</v>
+        <v>41639</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3547,34 +3547,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Arrondissement of Douai</t>
+          <t>Arrondissement of Mantes-la-Jolie</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Douai</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>50.37069</v>
+        <v>48.96523</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.07922</v>
+        <v>1.87314</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>252dc9b3-ab0a-55e9-873c-064f96c53ea6</t>
+          <t>5140a707-9f43-506f-868e-0bce2129328e</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_252dc9b3-ab0a-55e9-873c-064f96c53ea6_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_80000.0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>FR|Douai|renault|vehicle</t>
+          <t>FR|Flins-sur-Seine|renault|vehicle</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>('FR', 'Douai', 'renault', 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45291</v>
+        <v>44196</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_160000.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3714,21 +3714,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>novo mesto</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>novo_mesto</t>
+          <t>flins</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3755,22 +3755,34 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Flins-sur-Seine</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yvelines</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Arrondissement of Mantes-la-Jolie</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Flins-sur-Seine</t>
+        </is>
+      </c>
       <c r="P34" t="n">
-        <v>45.80397</v>
+        <v>48.96523</v>
       </c>
       <c r="Q34" t="n">
-        <v>15.16886</v>
+        <v>1.87314</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3779,48 +3791,48 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>cae893de-e792-5121-b6a8-75f1cf517027</t>
+          <t>5140a707-9f43-506f-868e-0bce2129328e</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_cae893de-e792-5121-b6a8-75f1cf517027_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5140a707-9f43-506f-868e-0bce2129328e_0.0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SI|Novo Mesto|renault|vehicle</t>
+          <t>FR|Flins-sur-Seine|renault|vehicle</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>('SI', 'Novo Mesto', 'renault', 'vehicle')</t>
+          <t>('FR', 'Flins-sur-Seine', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>martorell</t>
+          <t>novo mesto</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>martorell</t>
+          <t>novo_mesto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3833,7 +3845,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44197</v>
+        <v>44196</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3847,30 +3859,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Martorell</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Catalonia</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Martorell</t>
-        </is>
-      </c>
+          <t>Novo Mesto</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>41.47402</v>
+        <v>45.80397</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.93062</v>
+        <v>15.16886</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3879,48 +3883,48 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>fd4bfcba-5859-5681-a582-2f56b17afe5d</t>
+          <t>cae893de-e792-5121-b6a8-75f1cf517027</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_fd4bfcba-5859-5681-a582-2f56b17afe5d_80000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_cae893de-e792-5121-b6a8-75f1cf517027_40000.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>ES|Martorell|seat|vehicle</t>
+          <t>SI|Novo Mesto|renault|vehicle</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>('ES', 'Martorell', 'seat', 'vehicle')</t>
+          <t>('SI', 'Novo Mesto', 'renault', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>skoda</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mladá boleslav</t>
+          <t>martorell</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mladá_boleslav</t>
+          <t>martorell</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3933,7 +3937,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44075</v>
+        <v>44197</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3947,30 +3951,30 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Martorell</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Central Bohemia</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mladá Boleslav District</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Martorell</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>50.41135</v>
+        <v>41.47402</v>
       </c>
       <c r="Q36" t="n">
-        <v>14.90318</v>
+        <v>1.93062</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3979,61 +3983,61 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>f1bee7e3-ba81-5e19-b58b-196acd14eee5</t>
+          <t>fd4bfcba-5859-5681-a582-2f56b17afe5d</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f1bee7e3-ba81-5e19-b58b-196acd14eee5_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_fd4bfcba-5859-5681-a582-2f56b17afe5d_80000.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>CZ|Mladá Boleslav|skoda|vehicle</t>
+          <t>ES|Martorell|seat|vehicle</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>('CZ', 'Mladá Boleslav', 'skoda', 'vehicle')</t>
+          <t>('ES', 'Martorell', 'seat', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>skoda</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>mladá boleslav</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>poissy</t>
+          <t>mladá_boleslav</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45291</v>
+        <v>44075</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4047,34 +4051,30 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Poissy</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Central Bohemia</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Mladá Boleslav District</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Arrondissement of Saint-Germain-en-Laye</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Poissy</t>
-        </is>
-      </c>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>48.92902</v>
+        <v>50.41135</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.04952</v>
+        <v>14.90318</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4083,22 +4083,22 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1a826860-cc3f-5c7d-9e41-ab9563a927fc</t>
+          <t>f1bee7e3-ba81-5e19-b58b-196acd14eee5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_1a826860-cc3f-5c7d-9e41-ab9563a927fc_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f1bee7e3-ba81-5e19-b58b-196acd14eee5_120000.0</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>FR|Poissy|stellantis|vehicle</t>
+          <t>CZ|Mladá Boleslav|skoda|vehicle</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>('FR', 'Poissy', 'stellantis', 'vehicle')</t>
+          <t>('CZ', 'Mladá Boleslav', 'skoda', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4110,20 +4110,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>vigo</t>
+          <t>poissy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>40000</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>operational</t>
@@ -4131,11 +4133,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44502</v>
+        <v>44561</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4149,30 +4151,34 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Poissy</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Vigo</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>Arrondissement of Saint-Germain-en-Laye</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Poissy</t>
+        </is>
+      </c>
       <c r="P38" t="n">
-        <v>42.23282</v>
+        <v>48.92902</v>
       </c>
       <c r="Q38" t="n">
-        <v>-8.72264</v>
+        <v>2.04952</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4181,22 +4187,22 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>5ffe50f9-d148-5c9a-9d53-5afd17293ea1</t>
+          <t>1a826860-cc3f-5c7d-9e41-ab9563a927fc</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5ffe50f9-d148-5c9a-9d53-5afd17293ea1_nan</t>
+          <t>68d684fc1c2e9d8ed1487afa_1a826860-cc3f-5c7d-9e41-ab9563a927fc_40000.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>ES|Vigo|stellantis|vehicle</t>
+          <t>FR|Poissy|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>('ES', 'Vigo', 'stellantis', 'vehicle')</t>
+          <t>('FR', 'Poissy', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4328,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4335,7 +4341,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>41061</v>
+        <v>44562</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4386,7 +4392,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_5ffe50f9-d148-5c9a-9d53-5afd17293ea1_0.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_5ffe50f9-d148-5c9a-9d53-5afd17293ea1_80000.0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4435,7 +4441,7 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43831</v>
+        <v>45658</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4730,16 +4736,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5019,26 +5025,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tata jlr</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>tychy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>halewood</t>
+          <t>tychy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5051,7 +5057,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43101</v>
+        <v>44927</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5065,30 +5071,30 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Tychy</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Tychy</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Halewood</t>
+          <t>Tychy</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>53.36434</v>
+        <v>50.13717</v>
       </c>
       <c r="Q47" t="n">
-        <v>-2.82053</v>
+        <v>18.96641</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -5097,48 +5103,48 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>29be1890-3777-517a-a337-0b7c8b408704</t>
+          <t>6d7b9e8a-1e97-5e07-8020-e277406f26cc</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_29be1890-3777-517a-a337-0b7c8b408704_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d7b9e8a-1e97-5e07-8020-e277406f26cc_40000.0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>GB|Knowsley|tata jlr|vehicle</t>
+          <t>PL|Tychy|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>('GB', 'Knowsley', 'tata jlr', 'vehicle')</t>
+          <t>('PL', 'Tychy', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>grünheide</t>
+          <t>tychy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>grünheide</t>
+          <t>tychy</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5147,11 +5153,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>44561</v>
+        <v>45658</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5165,30 +5171,30 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Grünheide (Mark)</t>
+          <t>Tychy</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>Silesia</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Tychy</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Landkreis Oder-Spree</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Grünheide (Mark)</t>
-        </is>
-      </c>
+          <t>Tychy</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>52.42343</v>
+        <v>50.13717</v>
       </c>
       <c r="Q48" t="n">
-        <v>13.81324</v>
+        <v>18.96641</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5197,48 +5203,48 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>aa7e8a02-3dc6-59cf-bae6-5488cdc58c62</t>
+          <t>6d7b9e8a-1e97-5e07-8020-e277406f26cc</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_aa7e8a02-3dc6-59cf-bae6-5488cdc58c62_320000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_6d7b9e8a-1e97-5e07-8020-e277406f26cc_0.0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>DE|Grünheide (Mark)|tesla|vehicle</t>
+          <t>PL|Tychy|stellantis|vehicle</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>('DE', 'Grünheide (Mark)', 'tesla', 'vehicle')</t>
+          <t>('PL', 'Tychy', 'stellantis', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>tata jlr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hanover</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hanover</t>
+          <t>halewood</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5247,11 +5253,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>retrofit</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44926</v>
+        <v>43101</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5265,30 +5271,30 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Hanover</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Knowsley</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Region Hannover</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Hanover</t>
-        </is>
-      </c>
+          <t>Halewood</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>52.37052</v>
+        <v>53.36434</v>
       </c>
       <c r="Q49" t="n">
-        <v>9.733219999999999</v>
+        <v>-2.82053</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5297,48 +5303,48 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>f50f1baf-752f-5614-a4b3-9dc9071ee0e9</t>
+          <t>29be1890-3777-517a-a337-0b7c8b408704</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_f50f1baf-752f-5614-a4b3-9dc9071ee0e9_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_29be1890-3777-517a-a337-0b7c8b408704_20000.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>DE|Hanover|volkswagen|vehicle</t>
+          <t>GB|Knowsley|tata jlr|vehicle</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>('DE', 'Hanover', 'volkswagen', 'vehicle')</t>
+          <t>('GB', 'Knowsley', 'tata jlr', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>grünheide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>grünheide</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>20000</v>
+        <v>320000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5351,7 +5357,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43830</v>
+        <v>44561</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5365,22 +5371,30 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Grünheide (Mark)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Landkreis Oder-Spree</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Grünheide (Mark)</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>48.14816</v>
+        <v>52.42343</v>
       </c>
       <c r="Q50" t="n">
-        <v>17.10674</v>
+        <v>13.81324</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5389,22 +5403,22 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
+          <t>aa7e8a02-3dc6-59cf-bae6-5488cdc58c62</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_20000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_aa7e8a02-3dc6-59cf-bae6-5488cdc58c62_320000.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|volkswagen|vehicle</t>
+          <t>DE|Grünheide (Mark)|tesla|vehicle</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
+          <t>('DE', 'Grünheide (Mark)', 'tesla', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5416,21 +5430,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>hanover</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bratislava</t>
+          <t>hanover</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>140000</v>
+        <v>40000</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5439,11 +5453,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5457,22 +5471,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Hanover</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Region Hannover</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>48.14816</v>
+        <v>52.37052</v>
       </c>
       <c r="Q51" t="n">
-        <v>17.10674</v>
+        <v>9.733219999999999</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5481,48 +5503,48 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
+          <t>f50f1baf-752f-5614-a4b3-9dc9071ee0e9</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_140000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_f50f1baf-752f-5614-a4b3-9dc9071ee0e9_40000.0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SK|Bratislava Region|volkswagen|vehicle</t>
+          <t>DE|Hanover|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
+          <t>('DE', 'Hanover', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>volvo</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>torslanda</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5531,11 +5553,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>greenfield</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45657</v>
+        <v>43830</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5549,30 +5571,22 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Gothenburg Municipality</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Gothenburg Municipality</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Torslanda</t>
-        </is>
-      </c>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>57.72504</v>
+        <v>48.14816</v>
       </c>
       <c r="Q52" t="n">
-        <v>11.76903</v>
+        <v>17.10674</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5581,48 +5595,48 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>018941f9-89ca-5292-bb96-95fcd1445d4f</t>
+          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_018941f9-89ca-5292-bb96-95fcd1445d4f_120000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_20000.0</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SE|Gothenburg Municipality|volvo|vehicle</t>
+          <t>SK|Bratislava Region|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>('SE', 'Gothenburg Municipality', 'volvo', 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>volvo</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>bratislava</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5631,11 +5645,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44196</v>
+        <v>45291</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5649,34 +5663,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Arrondissement of Ghent</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Flanders</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>East Flanders Province</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Arrondissement of Ghent</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>51.05</v>
+        <v>48.14816</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.71667</v>
+        <v>17.10674</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5685,22 +5687,22 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>8727a516-7052-5f8b-a9da-0c21cb46ec42</t>
+          <t>87caa632-7c5c-5e67-947b-59d0a19b7cd2</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>68d684fc1c2e9d8ed1487afa_8727a516-7052-5f8b-a9da-0c21cb46ec42_40000.0</t>
+          <t>68d684fc1c2e9d8ed1487afa_87caa632-7c5c-5e67-947b-59d0a19b7cd2_140000.0</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>BE|Arrondissement of Ghent|volvo|vehicle</t>
+          <t>SK|Bratislava Region|volkswagen|vehicle</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>('BE', 'Arrondissement of Ghent', 'volvo', 'vehicle')</t>
+          <t>('SK', 'Bratislava Region', 'volkswagen', 'vehicle')</t>
         </is>
       </c>
     </row>
@@ -5712,21 +5714,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ghent</t>
+          <t>torslanda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5735,7 +5737,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -5753,56 +5755,260 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t>Gothenburg Municipality</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Gothenburg Municipality</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Torslanda</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>57.72504</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>11.76903</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>018941f9-89ca-5292-bb96-95fcd1445d4f</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_018941f9-89ca-5292-bb96-95fcd1445d4f_120000.0</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SE|Gothenburg Municipality|volvo|vehicle</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>('SE', 'Gothenburg Municipality', 'volvo', 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>volvo</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>greenfield</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>44196</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>Arrondissement of Ghent</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Flanders</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>East Flanders Province</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Arrondissement of Ghent</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Gent</t>
         </is>
       </c>
-      <c r="P54" t="n">
+      <c r="P55" t="n">
         <v>51.05</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q55" t="n">
         <v>3.71667</v>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>8727a516-7052-5f8b-a9da-0c21cb46ec42</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa_8727a516-7052-5f8b-a9da-0c21cb46ec42_40000.0</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>BE|Arrondissement of Ghent|volvo|vehicle</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>('BE', 'Arrondissement of Ghent', 'volvo', 'vehicle')</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>volvo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ghent</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Flanders</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>East Flanders Province</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Arrondissement of Ghent</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.71667</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>68d684fc1c2e9d8ed1487afa</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>8727a516-7052-5f8b-a9da-0c21cb46ec42</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
         <is>
           <t>68d684fc1c2e9d8ed1487afa_8727a516-7052-5f8b-a9da-0c21cb46ec42_200000.0</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>BE|Arrondissement of Ghent|volvo|vehicle</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>('BE', 'Arrondissement of Ghent', 'volvo', 'vehicle')</t>
         </is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45657</v>
+        <v>45292</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44561</v>
+        <v>44203</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4944,16 +4944,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45291</v>
+        <v>44196</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -4845,11 +4845,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>greenfield</t>
+          <t>retrofit</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reconcile/storage/input/zev_og_clean.xlsx
+++ b/reconcile/storage/input/zev_og_clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="397">
   <si>
     <t>inst_canon</t>
   </si>
@@ -91,9 +91,6 @@
     <t>ford</t>
   </si>
   <si>
-    <t>ford otosan</t>
-  </si>
-  <si>
     <t>hyundai</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>valencia</t>
   </si>
   <si>
-    <t>dolj</t>
-  </si>
-  <si>
     <t>nošovice</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>ES</t>
   </si>
   <si>
-    <t>RO</t>
-  </si>
-  <si>
     <t>CZ</t>
   </si>
   <si>
@@ -700,9 +691,6 @@
     <t>26f59fae-a89f-599f-94d0-a4e53b275c21</t>
   </si>
   <si>
-    <t>aeb6b6a5-e09a-5aeb-8372-eab9c4d2c261</t>
-  </si>
-  <si>
     <t>60d7afdf-9005-53df-ab21-93ee3d549c47</t>
   </si>
   <si>
@@ -844,9 +832,6 @@
     <t>68d684fc1c2e9d8ed1487afa_26f59fae-a89f-599f-94d0-a4e53b275c21_80000.0</t>
   </si>
   <si>
-    <t>68d684fc1c2e9d8ed1487afa_aeb6b6a5-e09a-5aeb-8372-eab9c4d2c261_0.0</t>
-  </si>
-  <si>
     <t>68d684fc1c2e9d8ed1487afa_60d7afdf-9005-53df-ab21-93ee3d549c47_120000.0</t>
   </si>
   <si>
@@ -997,9 +982,6 @@
     <t>ES|Valencia|ford|vehicle</t>
   </si>
   <si>
-    <t>RO|None|ford otosan|vehicle</t>
-  </si>
-  <si>
     <t>CZ|Nošovice|hyundai|vehicle</t>
   </si>
   <si>
@@ -1127,9 +1109,6 @@
   </si>
   <si>
     <t>('ES', 'Valencia', 'ford', 'vehicle')</t>
-  </si>
-  <si>
-    <t>('RO', 'None', 'ford otosan', 'vehicle')</t>
   </si>
   <si>
     <t>('CZ', 'Nošovice', 'hyundai', 'vehicle')</t>
@@ -1587,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1663,37 +1642,37 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2">
         <v>40000</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2">
         <v>45657</v>
       </c>
       <c r="I2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P2">
         <v>47.68333</v>
@@ -1702,19 +1681,19 @@
         <v>17.63512</v>
       </c>
       <c r="R2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="T2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="U2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="V2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1722,43 +1701,43 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>80000</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2">
         <v>43252</v>
       </c>
       <c r="I3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" t="s">
         <v>104</v>
       </c>
-      <c r="J3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" t="s">
-        <v>107</v>
-      </c>
       <c r="L3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P3">
         <v>50.85045</v>
@@ -1767,19 +1746,19 @@
         <v>4.34878</v>
       </c>
       <c r="R3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="T3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="U3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="V3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1787,46 +1766,46 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>20000</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H4" s="2">
         <v>45292</v>
       </c>
       <c r="I4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" t="s">
         <v>105</v>
       </c>
-      <c r="K4" t="s">
-        <v>108</v>
-      </c>
       <c r="L4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P4">
         <v>48.76508</v>
@@ -1835,19 +1814,19 @@
         <v>11.42372</v>
       </c>
       <c r="R4" t="s">
+        <v>213</v>
+      </c>
+      <c r="S4" t="s">
         <v>216</v>
       </c>
-      <c r="S4" t="s">
-        <v>219</v>
-      </c>
       <c r="T4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="U4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="V4" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1855,46 +1834,46 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>40000</v>
       </c>
       <c r="F5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" t="s">
         <v>98</v>
-      </c>
-      <c r="G5" t="s">
-        <v>101</v>
       </c>
       <c r="H5" s="2">
         <v>43983</v>
       </c>
       <c r="I5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P5">
         <v>49.18912</v>
@@ -1903,19 +1882,19 @@
         <v>9.22527</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="T5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="U5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="V5" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1923,46 +1902,46 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>80000</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2">
         <v>45744</v>
       </c>
       <c r="I6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P6">
         <v>49.01513</v>
@@ -1971,19 +1950,19 @@
         <v>12.10161</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="T6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="U6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="V6" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1991,46 +1970,46 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>180000</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2">
         <v>45657</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P7">
         <v>48.64244</v>
@@ -2039,19 +2018,19 @@
         <v>12.49283</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="U7" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="V7" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -2059,46 +2038,46 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H8" s="2">
         <v>45291</v>
       </c>
       <c r="I8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="T8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="U8" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="V8" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -2106,46 +2085,46 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>160000</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2">
         <v>44876</v>
       </c>
       <c r="I9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P9">
         <v>49.01513</v>
@@ -2154,19 +2133,19 @@
         <v>12.10161</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="T9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="U9" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="V9" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -2174,46 +2153,46 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>40000</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2">
         <v>42185</v>
       </c>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P10">
         <v>48.13743</v>
@@ -2222,19 +2201,19 @@
         <v>11.57549</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="T10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="U10" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="V10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2242,46 +2221,46 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>40000</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H11" s="2">
         <v>42370</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P11">
         <v>48.64244</v>
@@ -2290,19 +2269,19 @@
         <v>12.49283</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="U11" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="V11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2310,43 +2289,43 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>80000</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H12" s="2">
         <v>42369</v>
       </c>
       <c r="I12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P12">
         <v>51.33962</v>
@@ -2355,19 +2334,19 @@
         <v>12.37129</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="T12" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="U12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="V12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2375,43 +2354,43 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>40000</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2">
         <v>45657</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P13">
         <v>51.33962</v>
@@ -2420,19 +2399,19 @@
         <v>12.37129</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S13" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="T13" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="U13" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="V13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2440,46 +2419,46 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>160000</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2">
         <v>44742</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P14">
         <v>48.13743</v>
@@ -2488,19 +2467,19 @@
         <v>11.57549</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="T14" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="U14" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="V14" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2508,43 +2487,43 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>80000</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2">
         <v>43830</v>
       </c>
       <c r="I15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P15">
         <v>51.73213</v>
@@ -2553,19 +2532,19 @@
         <v>-1.20631</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S15" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="T15" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="U15" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="V15" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2573,43 +2552,43 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>80000</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2">
         <v>44196</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P16">
         <v>39.47391</v>
@@ -2618,19 +2597,19 @@
         <v>-0.37966</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="T16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U16" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="V16" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2638,46 +2617,64 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2">
-        <v>45657</v>
+        <v>43891</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="K17" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" t="s">
+        <v>149</v>
+      </c>
+      <c r="M17" t="s">
+        <v>171</v>
+      </c>
+      <c r="N17" t="s">
+        <v>113</v>
+      </c>
+      <c r="P17">
+        <v>49.66073</v>
+      </c>
+      <c r="Q17">
+        <v>18.42633</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="T17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U17" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="V17" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2685,64 +2682,64 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H18" s="2">
-        <v>43891</v>
+        <v>44196</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="M18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N18" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="P18">
-        <v>49.66073</v>
+        <v>49.22315</v>
       </c>
       <c r="Q18">
-        <v>18.42633</v>
+        <v>18.73941</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S18" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="T18" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="U18" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="V18" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2750,415 +2747,415 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19">
-        <v>60000</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2">
-        <v>44196</v>
+        <v>45261</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s">
-        <v>105</v>
-      </c>
-      <c r="K19" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" t="s">
-        <v>175</v>
-      </c>
-      <c r="N19" t="s">
-        <v>195</v>
-      </c>
-      <c r="P19">
-        <v>49.22315</v>
-      </c>
-      <c r="Q19">
-        <v>18.73941</v>
+        <v>102</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="T19" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="U19" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="V19" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2">
-        <v>45261</v>
+        <v>43831</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S20" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="T20" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="U20" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="V20" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" t="s">
         <v>98</v>
       </c>
-      <c r="G21" t="s">
-        <v>102</v>
-      </c>
       <c r="H21" s="2">
-        <v>43831</v>
+        <v>43102</v>
       </c>
       <c r="I21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J21" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
+        <v>115</v>
+      </c>
+      <c r="L21" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" t="s">
+        <v>173</v>
+      </c>
+      <c r="N21" t="s">
+        <v>193</v>
+      </c>
+      <c r="O21" t="s">
+        <v>115</v>
+      </c>
+      <c r="P21">
+        <v>48.85851</v>
+      </c>
+      <c r="Q21">
+        <v>8.20965</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="T21" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="U21" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="V21" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E22">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2">
-        <v>43102</v>
+        <v>42370</v>
       </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P22">
-        <v>48.85851</v>
+        <v>48.7</v>
       </c>
       <c r="Q22">
-        <v>8.20965</v>
+        <v>9.01667</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S22" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="T22" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="U22" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="V22" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E23">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="F23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" t="s">
         <v>98</v>
       </c>
-      <c r="G23" t="s">
-        <v>102</v>
-      </c>
       <c r="H23" s="2">
-        <v>42370</v>
+        <v>42005</v>
       </c>
       <c r="I23" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s">
-        <v>149</v>
-      </c>
-      <c r="M23" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P23">
-        <v>48.7</v>
+        <v>53.07582</v>
       </c>
       <c r="Q23">
-        <v>9.01667</v>
+        <v>8.807169999999999</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S23" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="T23" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="U23" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="V23" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E24">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F24" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" t="s">
         <v>98</v>
       </c>
-      <c r="G24" t="s">
-        <v>101</v>
-      </c>
       <c r="H24" s="2">
-        <v>42005</v>
+        <v>44530</v>
       </c>
       <c r="I24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s">
-        <v>153</v>
-      </c>
-      <c r="N24" t="s">
-        <v>198</v>
-      </c>
-      <c r="O24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P24">
-        <v>53.07582</v>
+        <v>46.90618</v>
       </c>
       <c r="Q24">
-        <v>8.807169999999999</v>
+        <v>19.69128</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S24" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="T24" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="U24" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="V24" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2">
-        <v>44530</v>
+        <v>43617</v>
       </c>
       <c r="I25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L25" t="s">
-        <v>121</v>
+        <v>151</v>
+      </c>
+      <c r="M25" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" t="s">
+        <v>119</v>
       </c>
       <c r="P25">
-        <v>46.90618</v>
+        <v>42.84998</v>
       </c>
       <c r="Q25">
-        <v>19.69128</v>
+        <v>-2.67268</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S25" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="T25" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="U25" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="V25" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -3166,64 +3163,61 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E26">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H26" s="2">
-        <v>43617</v>
+        <v>41275</v>
       </c>
       <c r="I26" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L26" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="M26" t="s">
-        <v>177</v>
-      </c>
-      <c r="N26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P26">
-        <v>42.84998</v>
+        <v>54.90465</v>
       </c>
       <c r="Q26">
-        <v>-2.67268</v>
+        <v>-1.38222</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="T26" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="U26" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="V26" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -3231,108 +3225,114 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E27">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H27" s="2">
-        <v>41275</v>
+        <v>40908</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M27" t="s">
-        <v>123</v>
+        <v>175</v>
+      </c>
+      <c r="N27" t="s">
+        <v>196</v>
+      </c>
+      <c r="O27" t="s">
+        <v>121</v>
       </c>
       <c r="P27">
-        <v>54.90465</v>
+        <v>50.27875</v>
       </c>
       <c r="Q27">
-        <v>-1.38222</v>
+        <v>3.97267</v>
       </c>
       <c r="R27" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="T27" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="U27" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="V27" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E28">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2">
-        <v>40908</v>
+        <v>45291</v>
       </c>
       <c r="I28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N28" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P28">
         <v>50.27875</v>
@@ -3341,270 +3341,270 @@
         <v>3.97267</v>
       </c>
       <c r="R28" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S28" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="T28" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="U28" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="V28" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E29">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H29" s="2">
-        <v>45291</v>
+        <v>43830</v>
       </c>
       <c r="I29" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P29">
-        <v>50.27875</v>
+        <v>49.17372</v>
       </c>
       <c r="Q29">
-        <v>3.97267</v>
+        <v>5.96869</v>
       </c>
       <c r="R29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S29" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="T29" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="U29" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="V29" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H30" s="2">
-        <v>43830</v>
+        <v>44926</v>
       </c>
       <c r="I30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J30" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L30" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M30" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="N30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P30">
-        <v>49.17372</v>
+        <v>50.37069</v>
       </c>
       <c r="Q30">
-        <v>5.96869</v>
+        <v>3.07922</v>
       </c>
       <c r="R30" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S30" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="T30" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="U30" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="V30" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E31">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="F31" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" t="s">
         <v>98</v>
       </c>
-      <c r="G31" t="s">
-        <v>102</v>
-      </c>
       <c r="H31" s="2">
-        <v>44926</v>
+        <v>41639</v>
       </c>
       <c r="I31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N31" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P31">
-        <v>50.37069</v>
+        <v>48.96523</v>
       </c>
       <c r="Q31">
-        <v>3.07922</v>
+        <v>1.87314</v>
       </c>
       <c r="R31" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="T31" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="U31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="V31" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E32">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="F32" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" t="s">
         <v>98</v>
       </c>
-      <c r="G32" t="s">
-        <v>101</v>
-      </c>
       <c r="H32" s="2">
-        <v>41639</v>
+        <v>44196</v>
       </c>
       <c r="I32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L32" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N32" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P32">
         <v>48.96523</v>
@@ -3613,66 +3613,66 @@
         <v>1.87314</v>
       </c>
       <c r="R32" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S32" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="T32" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="U32" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="V32" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E33">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="2">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K33" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L33" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N33" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O33" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P33">
         <v>48.96523</v>
@@ -3681,87 +3681,78 @@
         <v>1.87314</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S33" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="T33" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="U33" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="V33" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="F34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H34" s="2">
-        <v>45657</v>
+        <v>44196</v>
       </c>
       <c r="I34" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J34" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L34" t="s">
-        <v>157</v>
-      </c>
-      <c r="M34" t="s">
-        <v>180</v>
-      </c>
-      <c r="N34" t="s">
-        <v>202</v>
-      </c>
-      <c r="O34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P34">
-        <v>48.96523</v>
+        <v>45.80397</v>
       </c>
       <c r="Q34">
-        <v>1.87314</v>
+        <v>15.16886</v>
       </c>
       <c r="R34" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S34" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="T34" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="U34" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="V34" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3769,58 +3760,64 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E35">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H35" s="2">
-        <v>44196</v>
+        <v>44197</v>
       </c>
       <c r="I35" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J35" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>155</v>
+      </c>
+      <c r="M35" t="s">
+        <v>178</v>
+      </c>
+      <c r="N35" t="s">
+        <v>126</v>
       </c>
       <c r="P35">
-        <v>45.80397</v>
+        <v>41.47402</v>
       </c>
       <c r="Q35">
-        <v>15.16886</v>
+        <v>1.93062</v>
       </c>
       <c r="R35" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="T35" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U35" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="V35" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3828,64 +3825,64 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H36" s="2">
-        <v>44197</v>
+        <v>44075</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M36" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P36">
-        <v>41.47402</v>
+        <v>50.41135</v>
       </c>
       <c r="Q36">
-        <v>1.93062</v>
+        <v>14.90318</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S36" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T36" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="U36" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="V36" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3893,708 +3890,708 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E37">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="F37" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" t="s">
         <v>98</v>
       </c>
-      <c r="G37" t="s">
-        <v>102</v>
-      </c>
       <c r="H37" s="2">
-        <v>44075</v>
+        <v>44561</v>
       </c>
       <c r="I37" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L37" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N37" t="s">
-        <v>130</v>
+        <v>200</v>
+      </c>
+      <c r="O37" t="s">
+        <v>128</v>
       </c>
       <c r="P37">
-        <v>50.41135</v>
+        <v>48.92902</v>
       </c>
       <c r="Q37">
-        <v>14.90318</v>
+        <v>2.04952</v>
       </c>
       <c r="R37" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S37" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="T37" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="U37" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="V37" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E38">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H38" s="2">
-        <v>44561</v>
+        <v>43559</v>
       </c>
       <c r="I38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J38" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L38" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="M38" t="s">
         <v>180</v>
       </c>
       <c r="N38" t="s">
-        <v>203</v>
-      </c>
-      <c r="O38" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="P38">
-        <v>48.92902</v>
+        <v>48.37741</v>
       </c>
       <c r="Q38">
-        <v>2.04952</v>
+        <v>17.58723</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S38" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="T38" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="U38" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="V38" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>80000</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H39" s="2">
-        <v>43559</v>
+        <v>44562</v>
       </c>
       <c r="I39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="M39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N39" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="P39">
-        <v>48.37741</v>
+        <v>42.23282</v>
       </c>
       <c r="Q39">
-        <v>17.58723</v>
+        <v>-8.72264</v>
       </c>
       <c r="R39" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S39" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="T39" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="U39" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V39" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E40">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H40" s="2">
-        <v>44562</v>
+        <v>45658</v>
       </c>
       <c r="I40" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J40" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s">
-        <v>160</v>
-      </c>
-      <c r="M40" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="N40" t="s">
-        <v>133</v>
+        <v>202</v>
+      </c>
+      <c r="O40" t="s">
+        <v>131</v>
       </c>
       <c r="P40">
-        <v>42.23282</v>
+        <v>50.9807</v>
       </c>
       <c r="Q40">
-        <v>-8.72264</v>
+        <v>10.31522</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S40" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="T40" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="U40" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="V40" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H41" s="2">
-        <v>45658</v>
+        <v>44742</v>
       </c>
       <c r="I41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s">
-        <v>161</v>
+        <v>148</v>
+      </c>
+      <c r="M41" t="s">
+        <v>132</v>
       </c>
       <c r="N41" t="s">
-        <v>205</v>
-      </c>
-      <c r="O41" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="P41">
-        <v>50.9807</v>
+        <v>53.27875</v>
       </c>
       <c r="Q41">
-        <v>10.31522</v>
+        <v>-2.90134</v>
       </c>
       <c r="R41" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S41" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="T41" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="U41" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="V41" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F42" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" t="s">
         <v>98</v>
       </c>
-      <c r="G42" t="s">
-        <v>103</v>
-      </c>
       <c r="H42" s="2">
-        <v>44742</v>
+        <v>45292</v>
       </c>
       <c r="I42" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J42" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="M42" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s">
-        <v>206</v>
+        <v>204</v>
+      </c>
+      <c r="O42" t="s">
+        <v>133</v>
       </c>
       <c r="P42">
-        <v>53.27875</v>
+        <v>47.50808</v>
       </c>
       <c r="Q42">
-        <v>-2.90134</v>
+        <v>6.82748</v>
       </c>
       <c r="R42" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S42" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="T42" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="U42" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="V42" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E43">
         <v>40000</v>
       </c>
       <c r="F43" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" t="s">
         <v>98</v>
       </c>
-      <c r="G43" t="s">
-        <v>101</v>
-      </c>
       <c r="H43" s="2">
-        <v>45292</v>
+        <v>44203</v>
       </c>
       <c r="I43" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="M43" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P43">
-        <v>47.50808</v>
+        <v>50.26306</v>
       </c>
       <c r="Q43">
-        <v>6.82748</v>
+        <v>3.31358</v>
       </c>
       <c r="R43" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S43" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="T43" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="U43" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="V43" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E44">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="F44" t="s">
+        <v>95</v>
+      </c>
+      <c r="G44" t="s">
         <v>98</v>
       </c>
-      <c r="G44" t="s">
-        <v>101</v>
-      </c>
       <c r="H44" s="2">
-        <v>44203</v>
+        <v>44926</v>
       </c>
       <c r="I44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J44" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M44" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P44">
-        <v>50.26306</v>
+        <v>47.75205</v>
       </c>
       <c r="Q44">
-        <v>3.31358</v>
+        <v>7.32866</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S44" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T44" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="U44" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="V44" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E45">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="F45" t="s">
+        <v>95</v>
+      </c>
+      <c r="G45" t="s">
         <v>98</v>
       </c>
-      <c r="G45" t="s">
-        <v>101</v>
-      </c>
       <c r="H45" s="2">
-        <v>44926</v>
+        <v>44196</v>
       </c>
       <c r="I45" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J45" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="M45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N45" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P45">
-        <v>47.75205</v>
+        <v>48.11198</v>
       </c>
       <c r="Q45">
-        <v>7.32866</v>
+        <v>-1.67429</v>
       </c>
       <c r="R45" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S45" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="T45" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="U45" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="V45" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E46">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H46" s="2">
-        <v>44196</v>
+        <v>44927</v>
       </c>
       <c r="I46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M46" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="N46" t="s">
-        <v>210</v>
-      </c>
-      <c r="O46" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P46">
-        <v>48.11198</v>
+        <v>50.13717</v>
       </c>
       <c r="Q46">
-        <v>-1.67429</v>
+        <v>18.96641</v>
       </c>
       <c r="R46" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S46" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="T46" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="U46" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="V46" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E47">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H47" s="2">
-        <v>44927</v>
+        <v>45658</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P47">
         <v>50.13717</v>
@@ -4603,19 +4600,19 @@
         <v>18.96641</v>
       </c>
       <c r="R47" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S47" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="T47" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="U47" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="V47" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4623,64 +4620,64 @@
         <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H48" s="2">
-        <v>45658</v>
+        <v>43101</v>
       </c>
       <c r="I48" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J48" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L48" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="M48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N48" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="P48">
-        <v>50.13717</v>
+        <v>53.36434</v>
       </c>
       <c r="Q48">
-        <v>18.96641</v>
+        <v>-2.82053</v>
       </c>
       <c r="R48" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S48" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="T48" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="U48" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="V48" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -4688,64 +4685,64 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E49">
-        <v>20000</v>
+        <v>320000</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H49" s="2">
-        <v>43101</v>
+        <v>44561</v>
       </c>
       <c r="I49" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J49" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s">
-        <v>151</v>
-      </c>
-      <c r="M49" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="N49" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+      <c r="O49" t="s">
+        <v>139</v>
       </c>
       <c r="P49">
-        <v>53.36434</v>
+        <v>52.42343</v>
       </c>
       <c r="Q49">
-        <v>-2.82053</v>
+        <v>13.81324</v>
       </c>
       <c r="R49" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S49" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="T49" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="U49" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="V49" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4753,167 +4750,161 @@
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E50">
-        <v>320000</v>
+        <v>40000</v>
       </c>
       <c r="F50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" t="s">
         <v>98</v>
       </c>
-      <c r="G50" t="s">
-        <v>102</v>
-      </c>
       <c r="H50" s="2">
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="I50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N50" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P50">
-        <v>52.42343</v>
+        <v>52.37052</v>
       </c>
       <c r="Q50">
-        <v>13.81324</v>
+        <v>9.733219999999999</v>
       </c>
       <c r="R50" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S50" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="T50" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U50" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="V50" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E51">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H51" s="2">
-        <v>44926</v>
+        <v>43830</v>
       </c>
       <c r="I51" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J51" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s">
-        <v>166</v>
-      </c>
-      <c r="N51" t="s">
-        <v>213</v>
-      </c>
-      <c r="O51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P51">
-        <v>52.37052</v>
+        <v>48.14816</v>
       </c>
       <c r="Q51">
-        <v>9.733219999999999</v>
+        <v>17.10674</v>
       </c>
       <c r="R51" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S51" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T51" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="U51" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="V51" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E52">
-        <v>20000</v>
+        <v>140000</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H52" s="2">
-        <v>43830</v>
+        <v>45291</v>
       </c>
       <c r="I52" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J52" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K52" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L52" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P52">
         <v>48.14816</v>
@@ -4922,19 +4913,19 @@
         <v>17.10674</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="T52" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="U52" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="V52" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4942,170 +4933,179 @@
         <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E53">
-        <v>140000</v>
+        <v>120000</v>
       </c>
       <c r="F53" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H53" s="2">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="I53" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J53" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K53" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L53" t="s">
-        <v>144</v>
+        <v>164</v>
+      </c>
+      <c r="M53" t="s">
+        <v>142</v>
+      </c>
+      <c r="N53" t="s">
+        <v>211</v>
       </c>
       <c r="P53">
-        <v>48.14816</v>
+        <v>57.72504</v>
       </c>
       <c r="Q53">
-        <v>17.10674</v>
+        <v>11.76903</v>
       </c>
       <c r="R53" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S53" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="T53" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="U53" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="V53" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E54">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="F54" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H54" s="2">
-        <v>45657</v>
+        <v>44196</v>
       </c>
       <c r="I54" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J54" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K54" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L54" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M54" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="N54" t="s">
-        <v>214</v>
+        <v>143</v>
+      </c>
+      <c r="O54" t="s">
+        <v>212</v>
       </c>
       <c r="P54">
-        <v>57.72504</v>
+        <v>51.05</v>
       </c>
       <c r="Q54">
-        <v>11.76903</v>
+        <v>3.71667</v>
       </c>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S54" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="T54" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="U54" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="V54" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E55">
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="F55" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H55" s="2">
-        <v>44196</v>
+        <v>45657</v>
       </c>
       <c r="I55" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J55" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L55" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M55" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O55" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P55">
         <v>51.05</v>
@@ -5114,87 +5114,19 @@
         <v>3.71667</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S55" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="T55" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="U55" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="V55" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22">
-      <c r="A56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>87</v>
-      </c>
-      <c r="E56">
-        <v>200000</v>
-      </c>
-      <c r="F56" t="s">
-        <v>98</v>
-      </c>
-      <c r="G56" t="s">
-        <v>103</v>
-      </c>
-      <c r="H56" s="2">
-        <v>45657</v>
-      </c>
-      <c r="I56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J56" t="s">
-        <v>105</v>
-      </c>
-      <c r="K56" t="s">
-        <v>146</v>
-      </c>
-      <c r="L56" t="s">
-        <v>168</v>
-      </c>
-      <c r="M56" t="s">
-        <v>188</v>
-      </c>
-      <c r="N56" t="s">
-        <v>146</v>
-      </c>
-      <c r="O56" t="s">
-        <v>215</v>
-      </c>
-      <c r="P56">
-        <v>51.05</v>
-      </c>
-      <c r="Q56">
-        <v>3.71667</v>
-      </c>
-      <c r="R56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S56" t="s">
-        <v>260</v>
-      </c>
-      <c r="T56" t="s">
-        <v>315</v>
-      </c>
-      <c r="U56" t="s">
-        <v>359</v>
-      </c>
-      <c r="V56" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
